--- a/proposal/chuangzhihui-6600-proposal.xlsx
+++ b/proposal/chuangzhihui-6600-proposal.xlsx
@@ -8,14 +8,17 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 关键信息" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 楼层产品" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 招商策略" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 节点排期" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05 品牌活动" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06 收费项建议(核心)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 报价测算" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08 政策结合" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09 风险应对" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 楼层平面-3F" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 楼层平面-5F" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 杨浦政策清单" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05 火山引擎折扣" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06 招商策略" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 三年排期" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08 合作报价(核心)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09 媒体报价" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10 报价测算" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11 规划与拓展" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 风险应对" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,6 +47,11 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="10.5"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -99,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -110,7 +118,13 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -478,11 +492,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="78" customWidth="1" min="2" max="2"/>
+    <col width="82" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -510,19 +524,19 @@
           <t>项目位置</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>上海市杨浦区五角场附近 · 创智汇(创智天地片区)</t>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>上海市杨浦区五角场附近 · 创智汇（创智天地片区）</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>合作面积</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>约 6600㎡</t>
         </is>
@@ -534,19 +548,19 @@
           <t>3 楼(约 2850㎡)</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>孵化器 + 办公（AI / OPC 主轴）</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>5 楼(约 3670㎡)</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>展厅 + 贸易（IP 内容主轴）</t>
         </is>
@@ -555,84 +569,505 @@
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>项目属性</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>产业空间 + 科创合作空间 + 企业招商运营空间</t>
+          <t>合作周期</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>3 年 · 可复制 · 协同周边 ≤2 个项目</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>合作方向</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>产业招商、空间运营、企业服务、政策服务、IP 内容与出海</t>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>合作方式</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>对赌运营（收基础运营费 + 对赌去化）</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
+          <t>项目属性</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>产业空间 + 科创合作空间 + 企业招商运营空间</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
           <t>核心价值</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>区位 + 杨浦科创资源 + 高校人才 + 产业政策 + 城市更新空间价值</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>定位主线</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>超级链接器：IP 为内容、AI 为工具、空间为载体</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
+          <t>定位主线</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>超级链接器：IP 为内容、AI 为工具、空间为载体</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
           <t>三大集群</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>动漫 IP、科技应用、交互设计</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>可链接资源</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>北大上海校友会、同济设计创新院、科企联、IP/玩具/广告协会、混知等 IP、聚成智能、中建四局</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>关键变量</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>离我方极近(20–30 分钟)→ 支撑「轻驻场、高频次」运营，是盈利关键</t>
+          <t>政策卡位</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>正处杨浦 YOUNG立方「一楼(V聚场)·一街(大学路)·一园(B站新世代产业园)·一区」核心圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>可链接资源</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>北大上海校友会、同济设计创新院、复旦科技园、科企联、IP/玩具/广告协会、混知等 IP、聚成智能、中建四局</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>07 · 报价测算 · 对方视角</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>项目</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>口径 / 金额</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>固定服务包(年)</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>约 95 万/年</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>基础运营 60 万 + 活动 30 万 + 媒体 5 万</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>招商佣金(浮动)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>成交后 2–3 个月租金</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>首年不重复计算</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>挂牌费(浮动)</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>3 万/个</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>按数量与影响力分档；国际会议厅另计</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>增值服务(浮动)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>联合公司经营分成</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>工商/政策/知产/财税法务/融资/出海</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>补贴归属</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>归运营平台公司</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>协助申请，成功兑现为准</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>——对方测算——</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="inlineStr"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>对方空间成本</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>≈554 万/年</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>2.3 元/㎡/天 × 6600㎡ × 365</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>我方固定服务包</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>约 95 万/年 + 佣金</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>由对方利润/中建四局运营费列支，非纯增量</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>对方收益</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>去化率 60→70→85%、企业质量↑、政策承接、品牌示范</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>比照元谷「花一份钱赚四份钱」逻辑</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="84" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>08 · 规划建议与业务拓展</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>事项</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>建议</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>规划设计</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>配置 4–6 人设计条件；不建议做联合办公，突出产业办公与展贸</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>多元化收入</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>联合开展培训；利用小红书招募，增加经营性收入</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>资源导入</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>引入复旦科技园进行客户导流，形成稳定客源</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>空间利用</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>顶层部分可举办漫展或各类展览（门票 + 赞助）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>协同复制</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>合作模式可协同周边不超过两个项目，具备可复制性</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>业务拓展</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>以本项目为支点，进一步协助拓展新的合作项目</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="74" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>风险点与应对</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>风险</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>应对</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>空间合规（用途/消防/承重/用电）</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>入驻准入审核；以轻型研发/中试/装配/测试与办公展示为主，拒高污染高噪音高能耗</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>招商去化</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>先样板企业 + 首批优惠 + 高校/协会/社群/复旦科技园渠道 + 政策抓手；对赌 60/70/85%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>收益周期</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>基础运营费保障；佣金与去化挂钩；增值服务逐步导入，避免前期重投入</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>政策兑现</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>一切以政府最新文件为准；不承诺必得补贴；服务以辅导/申报/对接为主，成功费按实际兑现计</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>合作复制边界</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>协同周边 ≤2 个项目；单项目单核算，避免人力成本覆盖不住</t>
         </is>
       </c>
     </row>
@@ -652,247 +1087,201 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>03 · 楼层产品切分（招商最小颗粒度）</t>
+          <t>03 · 3 楼平面布局 · 孵化 + 办公 ≈ 2850㎡</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>楼层</t>
+          <t>功能分区</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>产品</t>
+          <t>房间号</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>面积区间</t>
+          <t>面积</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>数量建议</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>适合客户</t>
+          <t>定位 / 说明</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>3 楼 孵化+办公
-≈2850㎡(AI/OPC 主轴)</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>标准小单元</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>80–150㎡</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>8–12 个</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>AI 初创、设计团队、科技型小微</t>
+          <t>AI+IP 产业办公空间</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>301 / 302 / 303</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>1150㎡</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>整层主力办公，可分割多间</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="4" t="inlineStr"/>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>成长型单元</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>200–350㎡</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>3–4 个</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>AI 应用、研发设计、生产性服务</t>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>OPC 产业办公空间</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>304 / 305</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>700㎡</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>OPC 社群与 AI 项目办公</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="3" t="inlineStr"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>OPC 联合办公/工位</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>工位大区</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>1 个大区</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>AI 项目、黑客松团队、孵化项目</t>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>AI+IP 产业办公空间</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>306 / 310</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>600㎡</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>成长型企业办公</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="4" t="inlineStr"/>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>直播间 / AI 展示运营</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>共享</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>1–2 间</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>按次/按时段共享</t>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>AI 展示与运营</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>250㎡</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>AI 展示 / 运营位</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>5 楼 展厅+贸易
-≈3670㎡(IP 内容主轴)</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>综合集群展厅</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>700–900㎡</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>1 个</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>50+ IP 集中展示、轮展</t>
+          <t>直播间</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>150㎡</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>直播 / 内容生产</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="4" t="inlineStr"/>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>产业集群展位</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>270–700㎡/区</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>4–5 区</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>汕头玩具/扬州毛绒/东莞潮玩/文创</t>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>接待·前台·休闲区·茶水间</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>配套</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>接待 1 / 接待 2 / 前台 / 休闲区 ×2 / 茶水间</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="3" t="inlineStr"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IP 展销 / 跨境贸易</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>按摊位/面积</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>若干</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>IP 零售、跨境展销平台</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="4" t="inlineStr"/>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>培训沙龙 / 仓储</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>120–650㎡</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>各 1</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>OPC 社区培训、活动、样品仓储</t>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>≈2850㎡</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>OPC + AI + IP 创新中心整层运营</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
@@ -906,154 +1295,171 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>03 · 招商漏斗 + 务实目标</t>
+          <t>03 · 5 楼平面布局 · 展厅 + 贸易 ≈ 3670㎡</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>层级/项</t>
+          <t>功能分区</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>名称</t>
+          <t>面积</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>说明</t>
+          <t>内容 / 说明</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>牌照锚定</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>校友会/科企联/IP/玩具协会挂牌前置，客户「送进来」</t>
+          <t>综合集群展厅</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>900㎡</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>50+ IP 集中展示 · 轮展</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>政策招商</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>AI/大数据补贴续享 + 算力补贴 + 腾讯云作「入驻礼包」</t>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>AI+IP 展示中心</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>700㎡</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>AI 智能产业集群展示</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>L3</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>社群/活动带流</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>OPC 社群、黑客松、小红书投流、漫展、沙龙持续导流</t>
+          <t>玩具/毛绒/潮玩 产业集群</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>700㎡</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>汕头玩具 · 扬州毛绒 · 东莞潮玩</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>L4</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>资源转化</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>高校成果转化、IP 品牌方、链主配套、外贸玩具厂转化</t>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>文创产业集群</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>650㎡</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>景区 + 博物馆文创</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>目标</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>年去化达标线</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>2000–3000㎡（不设过高保底）</t>
+          <t>OPC 社区培训中心</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>330㎡</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>培训 / 社群活动</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>目标</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>对赌面积</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>对赌模式建议锁定 3300–4300㎡</t>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>休闲沙龙区</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>270㎡</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>沙龙 / 洽谈</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>客群</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>五类目标客户</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>AI 项目 / 潮玩玩具文创 IP / 科技型中小 / 高校成果转化 / 生产性服务业</t>
+          <t>仓储</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>120㎡</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>样品 / 货品仓储</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>≈3670㎡</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>顶层可办漫展 / 展览（门票 + 赞助）</t>
         </is>
       </c>
     </row>
@@ -1073,129 +1479,151 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="56" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>04 · 四阶段排期</t>
+          <t>04 · 杨浦政策清单（以政府最新文件为准）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>阶段</t>
+          <t>政策</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>时间窗口</t>
+          <t>赛道</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>目标</t>
+          <t>关键条款要点</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>重点动作</t>
+          <t>本项目用法</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>启动期</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>0–3 月</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>定位+政策+渠道</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>招商手册、收费标准、政策汇编、企业库、首批挂牌、1–2 家样板</t>
+          <t>YOUNG立方·18 条（2025）</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>互联网优质内容 / 微短剧</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>免：入孵 V聚场三年租金物业减免（全免/75%/50%）；补：直播券≤50万、活动≤50%（年≤200万）；投：≥10亿内容基金、贷款50%贴息、担保费率0.5%；人才：购房≤200万、公寓≤8000/月</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>5F IP 内容 / 微短剧对齐；作招商政策礼包与载体培育方向</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>导入期</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>3–6 月</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>首批入驻 30–50%</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>集中招引 AI/IP/潮玩、首批优惠、推介路演、政策诊断</t>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>长阳秀带·在线新经济</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>数字经济 / AI 大数据</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>AI 及大数据企业房租补贴 3 年每年≤100万；头部/总部≤1500万开办费；技术攻关研发投入10–30%≤200万；应用场景≤500万；10 亿母基金</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>3F AI 企业房租/研发/场景补贴，作核心招商抓手</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>成型期</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>6–12 月</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>提升出租率与质量</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>重点客户补位、专精特新/高企培育、企业服务收费、首场漫展</t>
+          <t>人工智能+ 行动（2026–2028）</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>六大赛道 / 内容生成</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>大模型垂类应用补贴≤50%、≤500万；AI 人才个人奖励≤30万；聚焦具身智能/类脑/智能终端/内容生成工具/量子/多智能体</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>3F AI 应用与孵化对齐，叠加算力与人才政策</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>提升期</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>12 月+</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>稳定收入与品牌</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>区级示范点、载体资质、活动 IP 化、出海撮合、模式复制</t>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>数字经济产业体系（指引）</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>三大千亿集群</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>在线新经济 · 智能制造 · 创意设计 三大千亿集群 + 科技服务/人工智能/生命健康/绿色低碳 四大新兴；专项资金「就高不重复」</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>产业定位对齐，便于配套市/区专项资金</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>算力补贴</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>算力 / AI</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>凭算力发票向科委/经信申请，最高补贴 50%</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>叠加火山引擎 / 腾讯云，打造专有算力政策包</t>
         </is>
       </c>
     </row>
@@ -1215,103 +1643,154 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="56" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>05 · 品牌与活动</t>
+          <t>04 · 火山引擎园区独立政策（优于火山工坊）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>板块</t>
+          <t>累计消费区间</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>内容</t>
+          <t>额外折扣（代金券之外）</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>金额 / 口径</t>
+          <t>说明</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>挂牌</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>北大上海校友会(优先)、科企联/科技服务中心、IP 协会、中国玩具协会</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>总包约 20–50 万</t>
+          <t>半年费用</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>无门槛免费</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>按预估半年费用一次性发放代金券</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>活动</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>20–24 场沙龙/路演/培训/发布会</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>打包约 30 万(+赞助/门票)</t>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>0 – 10 万</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>5 折 ~ 7 折</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>大客户额外折扣</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>漫展</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>千人级，门票+赞助；10–11 月首场，对接 BW 广告商与二次元资源</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>门票+赞助双收入</t>
+          <t>10 – 30 万</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>4.5 折 ~ 5 折</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>大客户额外折扣</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>北欧会客厅</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>海外 IP/技术入华 + 国内 IP 出海撮合台</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>收租金则不分出海；不收租金则撮合成交取分成(二选一)</t>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>30 – 50 万</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>4 折 ~ 4.5 折</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>大客户额外折扣</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>50 – 100 万</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>3.5 折 ~ 4 折</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>大客户额外折扣</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>100 – 300 万</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>3 折 ~ 3.5 折</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>大客户额外折扣</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>300 – 500 万+</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>2.5 折 ~ 3 折</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>累计消费越多，折扣越低</t>
         </is>
       </c>
     </row>
@@ -1331,179 +1810,143 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="74" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>06 · 五类收费项（收费项建议）</t>
+          <t>05 · 招商漏斗 + 三年目标</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>类别</t>
+          <t>层级/项</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>收费对象</t>
+          <t>名称</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>收费方式</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>建议金额 / 口径</t>
+          <t>说明</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>① 基础运营月费</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>合作方/项目公司</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>按月</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>市场 10–30 万/月；首报 12 万/月；对赌版 5–6 万/月(对赌 3300–4300㎡)；收月费即对赌去化</t>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>牌照锚定</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>校友会/科企联/IP/玩具协会挂牌前置，客户「送进来」</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>② 招商佣金</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>合作方/业主方</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>成交后</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>市场 2–3 个月年租金；我方抽 ≤1 个月，只给首月、不重复；返投/重点客户可另议</t>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>政策招商</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>杨浦政策 + 火山引擎 + 算力补贴，作「入驻礼包」</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>③ 挂牌费</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>合作方</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>一次性/按项</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>总包 20–50 万(北大校友会/科企联/IP 协会等，按数量与影响力分档)</t>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>社群/活动带流</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>OPC 社群、黑客松、小红书投流、漫展、沙龙、复旦科技园导流</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>④ 活动执行费</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>合作方+外部</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>按场/打包</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>20–24 场/年打包约 30 万；漫展门票+赞助、净利分成</t>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>资源转化</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>高校成果转化、IP 品牌方、链主配套、外贸玩具厂转化</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>⑤ 媒体流量费</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>合作方</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>按季度/项目</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>小红书投流、OPC 社群内容、短视频/直播间运营</t>
+          <t>目标</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>三年去化</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>首年 60% / 次年 70% / 第三年 85%（与基础运营费对赌）</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>⑥ 企业增值服务</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>入驻企业</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>按项/成功收费</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>工商注册、政策申报(科小备案/高企/专精特新/研发归集/技改)、知识产权、财税法务、融资、出海撮合</t>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>客群</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>五类目标客户</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>AI 项目 / 潮玩玩具文创 IP / 科技型中小 / 高校成果转化 / 生产性服务业</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
@@ -1517,163 +1960,86 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="68" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>06 · 打包报价示例 + 对方视角测算</t>
+          <t>06 · 三年运营排期</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>项目</t>
+          <t>阶段</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>口径 / 金额</t>
+          <t>去化目标</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>说明</t>
+          <t>重点动作</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>固定服务包(年)</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>约 110 万/年(可砍至~100 万)</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>月费 5 万×12=60 万 + 活动 30 万 + 挂牌 20 万</t>
+          <t>第 1 年 · 启动+导入</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>命名/招商手册/收费方案/政策汇编/首批挂牌/样板企业/首批招引 AI·IP·潮玩</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>招商佣金(浮动)</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>我方抽 ≤1 个月年租金</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>按实际去化另计，只给首月不重复</t>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>第 2 年 · 成型+提质</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>重点客户补位/专精特新·高企培育/企业服务收费/漫展与沙龙常态化</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>增值服务(浮动)</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>据实另计</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>政策申报、出海撮合分成、驻场运营费、媒体投流</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>政策申报参考</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>0.3–2 万/项；高企专精特新 2–8 万/项；补贴类到账额 5%–15%</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>成功费按实际兑现计</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>——对方测算——</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="3" t="inlineStr"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>对方空间成本</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>≈554 万/年</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>2.3 元/㎡/天 × 6600㎡ × 365，一天约 1.5 万+</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>我方服务包</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>100–120 万/年 + 招商佣金</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>由对方利润/中建四局运营费列支，非纯增量</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>对方收益</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>去化率↑、企业质量↑、政策承接、租金溢价、品牌示范</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>比照元谷「花一份钱赚四份钱」逻辑，账面可算正</t>
+          <t>第 3 年 · 提升+复制</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>区级示范点/载体资质/补贴反哺/协同周边≤2项目/模式可复制</t>
         </is>
       </c>
     </row>
@@ -1693,211 +2059,245 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>06 · 当地政策内容结合（以政府最新文件为准）</t>
+          <t>07 · 合作报价总表 · 五类收费</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>政策方向</t>
+          <t>收费项</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>结合方式 / 抓手</t>
+          <t>标准 / 口径</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>在本项目的用法</t>
+          <t>支付方</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>杨浦 AI/大数据补贴</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>存量延续：2025.2 到期，但已申报企业 3 年内可续享</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>作为招商引子，引导企业向我方靠拢</t>
+          <t>基础运营费</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>60 万/年（5 万/月）</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>合作方按月</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>支持对赌，与去化目标挂钩</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>算力补贴</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>凭算力发票向科委/经信申请，最高补贴 50%</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>打造「创智汇专有政策包」</t>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>对赌去化目标</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>首年 60% / 次年 70% / 第三年 85%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>达标机制，挂钩基础运营费</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>腾讯云 / 算力合作</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>新注册 AI 公司免 2 个月 / 算力 85 折</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>签约共建，叠加专有政策</t>
+          <t>人员配置</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>项目安排 2 人</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>含杨浦科技企业服务中心挂牌服务</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>科技型中小企业</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>辅导备案，为高企/研发加计扣除打基础</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>基础政策诊断(免费引流)</t>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>招商佣金</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>成交后 2–3 个月租金（首年不重复计算）</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>合作方</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>参照市场价</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>高新技术企业</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>研发投入/知识产权/科技人员比例辅导</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>增值收费项</t>
+          <t>挂牌费</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>单个 3 万元，按数量与影响力分档</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>合作方</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>国际会议厅费用另计</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>专精特新</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>创新型中小→市级专精特新→国家级小巨人</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>固定费+成功费</t>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>活动执行费</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>每年约 30 场，打包 30 万元（每场≥30 人）</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>合作方</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>含策划与执行</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>人才政策</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>落户、人才公寓、创业人才、毕业生招聘</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>企业服务包</t>
+          <t>媒体流量费</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>每年 5 万元</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>合作方</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>详见「媒体报价」分表</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>研发/技改</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>研发费用加计、技改、设备补贴、智能制造、数字化转型</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>工业/研发类企业适配</t>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>企业增值服务</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>工商注册/政策申报/知识产权/税收法务/融资/出海撮合</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>入驻企业</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>成立联合公司经营分成</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>创新创业载体</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>众创空间/孵化器/加速器/产业创新服务平台</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>争取载体认定，提升招商可信度</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>三层政策服务</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>基础诊断(免费) / 专项申报(收费) / 政府资源对接(深度)</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>招商工具 + 盈利工具</t>
+          <t>政府补贴与资质</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>协助申请相关政府补贴与企业资质</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>申请下的补贴归运营平台公司</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
@@ -1911,95 +2311,143 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>风险点与应对</t>
+          <t>07 · 媒体报价（基础包 5 万/年）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>风险</t>
+          <t>媒体项</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>应对</t>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>计费方式</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>空间合规(用途/消防/承重/用电)</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>入驻准入审核；以轻型研发/中试/装配/测试与办公展示为主，拒高污染高噪音高能耗</t>
+          <t>小红书投流</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>话题/笔记投放，招募与引流</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>含基础包 / 超额按量</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>招商去化</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>先样板企业 + 首批优惠 + 高校/协会/社群渠道 + 政策抓手；目标务实(年 2000–3000㎡)</t>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>账号代运营</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>园区及 IP 官方账号内容运营</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>含基础包</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>收益周期</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>初期设基础服务费/保底；佣金与去化挂钩；增值服务逐步导入，避免前期重投入</t>
+          <t>短视频 / 直播间</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>活动直播、企业专访、产品发布</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>含基础包 / 专场另计</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>政策兑现</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>一切以政府最新文件为准；不承诺必得补贴；服务以辅导/申报/对接为主，成功费按实际兑现计</t>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>新闻通稿 / 软文</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>招商节点媒体声量</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>按篇 / 按节点</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>月费被复制锁死</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>单项目单核算；多项目须重新议价，避免人力成本覆盖不住</t>
+          <t>专项传播</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>漫展 / 峰会 / 挂牌等大型节点传播</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>按项目另计</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>基础包合计</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>上述常态化运营打包</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>5 万元/年</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>

--- a/proposal/chuangzhihui-6600-proposal.xlsx
+++ b/proposal/chuangzhihui-6600-proposal.xlsx
@@ -11,14 +11,19 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 楼层平面-3F" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 楼层平面-5F" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 杨浦政策清单" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05 火山引擎折扣" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06 招商策略" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 三年排期" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08 合作报价(核心)" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09 媒体报价" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10 报价测算" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11 规划与拓展" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 风险应对" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04b 政策工具箱三端" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04c 后续摸排清单" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05 火山引擎折扣" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06 招商策略" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 三年排期" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08 合作报价(核心)" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09 媒体合作报价" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09b 配套政策-复旦杨浦" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09c 杨浦科创政策" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09d 微短剧措施" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10 报价测算" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11 规划与拓展" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 风险应对" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -678,6 +683,914 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>07 · 合作报价总表 · 五类收费</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>收费项</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>标准 / 口径</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>支付方</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>基础运营费</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>60 万/年（5 万/月）</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>合作方按月</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>支持对赌，与去化目标挂钩</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>对赌去化目标</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>首年 60% / 次年 70% / 第三年 85%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>达标机制，挂钩基础运营费</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>人员配置</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>项目安排 2 人</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>含杨浦科技企业服务中心挂牌服务</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>招商佣金</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>成交后 2–3 个月租金（首年不重复计算）</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>合作方</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>参照市场价</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>挂牌费</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>单个 3 万元，按数量与影响力分档</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>合作方</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>国际会议厅费用另计</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>活动执行费</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>每年约 30 场，打包 30 万元（每场≥30 人）</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>合作方</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>含策划与执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>媒体流量费</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>每年 5 万元</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>合作方</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>详见「媒体报价」分表</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>企业增值服务</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>工商注册/政策申报/知识产权/税收法务/融资/出海撮合</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>入驻企业</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>成立联合公司经营分成</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>政府补贴与资质</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>协助申请相关政府补贴与企业资质</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>申请下的补贴归运营平台公司</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>07 · 媒体合作报价（媒体服务协议）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>服务项目</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>原创内容生产</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>3 篇</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>结合项目品牌定位与内涵，品牌宣传稿 + 营销活动稿原创采写</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>中央级/全国性/上海主流媒体宣发</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>10 篇</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>央视新闻/央广网/人民网/新华网/中新网/第一财经/21世纪/澎湃/界面/中国日报/上证报等</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>全国社交平台流量投放</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>抖音、今日头条等信息流广告，投放区域上海（抖音短视频素材拍摄制作费不含）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>营销策划与舆情管理咨询</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>≤2 次</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>提供营销策划咨询，并配合协调处理媒体舆情</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>折后总价</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>5 万元（媒体总曝光量预计不低于 150 万）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>服务周期</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>自签约起至 2026.12.31；期满可续，乙方享优先续约权；内容可按宣传需要调整</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>交付物</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>合作结束提供完整投放报告（发布链接证明 + 曝光量证明 + 投放分析）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="56" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>配套政策 · 复旦科技园及杨浦区（园区代申报）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>政策类型</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>扶持标准（要点）</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>申报/审批</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>总部政策</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>外区新引进且税务落杨浦、区域贡献&gt;1000万：开办费≤500万，分三年 40%/30%/30%</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>园区申报，区商务委</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>高管人才/住房</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>高管购房补贴≤100万、租房≤10万；高层次人才月 500–1000 元（2 年）</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>园区申报</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>科技金融(上市)</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>N 板 50万 / 新三板 100万 / 主板 300万 / 创业板·中小板 200万</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>园区申报，区联审办</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>3310 海外高层次人才</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>A 类 100万 / B 类 60万 / C 类 30万；国家千人购房≤200万</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>企业向 3310 中心</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>知识产权</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>发明授权 800元/件、实用新型 500元/件；市级示范企业 5–10万</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>区科委，每年 7–8 月</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="40" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>创新基金/小巨人</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>市小巨人 200万 / 市培育 100万 / 区科技小巨人 50万 / 区双创小巨人 100万</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>园区向区科委推荐</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>服务业引导资金</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>重点项目≤总投入20%、≤300万；一般≤15%、≤200万</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>园区向区发改委推荐</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>文创基金</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>市级≤300万，支持比例≤总投资 50%</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>园区向区商委推荐</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>专精特新</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>市级 5万 / 区级 3万</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>企业向区中小企业服务中心</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="78" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>杨浦区科创企业政策支持方案（要点）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>政策</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>扶持标准</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>服务业发展引导资金</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>总投资≥500万项目，市区两级≤总投资20%、≤300万</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>文化创意产业专项</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>单项目市级≤300万；市区合计≤总投资50%（或按 LPR 50% 贴息）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>高新技术企业</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>首次认定 20万；新迁入 10万；重新认定 5万</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>专精特新中小企业</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>市级 10万；国家级小巨人 30万；国内外首次上市额外 20万</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>区级科技小巨人 / 双创小巨人</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>科技小巨人 50万；双创小巨人 100万</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>AI 与大数据房租补贴</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>2.0 元/天/㎡，面积按人均 15㎡ 计，补贴上限 100万</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>人才奖励</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>战略人才薪酬 8%、其他产业人才 5%，最高 30万；房租补贴≤8000/月</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>经营性奖励</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>择优≤30万；营收≥100万按≤10%奖励；营收增量部分≤10%奖励</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>参保人数奖励</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>10–20 人给 10万；超 20 人每多 1 人≤1.5万</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="84" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>上海市 AI 赋能微短剧高质量发展若干措施（要点）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>方向</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>要点</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>技术支撑</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>布局市级「AI+微短剧」中试基地；智能体项目按≤研发投入20%、≤1000万支持</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>核心要素</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>支持算力租用、视听大模型 API 调用、非关联方语料采购；建数字资产库/IP库</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>优质内容</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>国家级评选剧本一次性 5万；优秀微短剧≤300万；文商旅体展联动 +50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>公共服务</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>一站式服务中心（咨询/审查/协拍/版权/金融/出海）；备案随报随审</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>经营主体</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>优质厂牌≤200万；打造 AI 微短剧 OPC（一人公司）社区，释放超级个体+AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>文化出海</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>浦东建出海基地；出海企业≤50万</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>重点集聚区</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>在徐汇、杨浦、闵行建设 AI 微短剧产业集聚区，给予要素/项目/活动支持</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>人才引育</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>人才计划申报；课程培训每个课程≤20万；职称与技能评价通道</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -865,7 +1778,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -979,7 +1892,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1517,7 +2430,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1">
+    <row r="3" ht="58" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>YOUNG立方·18 条（2025）</t>
@@ -1539,7 +2452,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
+    <row r="4" ht="58" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
           <t>长阳秀带·在线新经济</t>
@@ -1561,7 +2474,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
+    <row r="5" ht="58" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>人工智能+ 行动（2026–2028）</t>
@@ -1583,7 +2496,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1">
+    <row r="6" ht="58" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>数字经济产业体系（指引）</t>
@@ -1605,7 +2518,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
+    <row r="7" ht="58" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>算力补贴</t>
@@ -1643,160 +2556,245 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>04 · 火山引擎园区独立政策（优于火山工坊）</t>
+          <t>04 · 人工智能+数字内容 政策工具箱（三端）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>累计消费区间</t>
+          <t>政策</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>额外折扣（代金券之外）</t>
+          <t>功能端</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
+          <t>关键要点 / 金额</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>有效周期 / 备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="66" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>半年费用</t>
+          <t>杨浦区加快科技服务业高质量发展若干措施</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>无门槛免费</t>
+          <t>载体端</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>按预估半年费用一次性发放代金券</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
+          <t>高质量孵化器/概念验证/中试平台建设；成果转化服务平台经认定≤100万/年运营补贴；场景清单经认定≤投资30%、≤500万</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>2026.4.21–2027.10.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="66" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>0 – 10 万</t>
+          <t>杨浦区服务业发展引导资金</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>5 折 ~ 7 折</t>
+          <t>企业端/载体端</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>大客户额外折扣</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
+          <t>支持服务业项目/园区/新业态；市级项目总投资≥500万，区级500–1000万；3F+5F 可论证为「AI 数字内容孵化展示交易服务平台」</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>邮箱截至2026.7.3；系统7.13–7.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="66" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>10 – 30 万</t>
+          <t>关于支持打造 OPC 超级个体社区若干措施</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>4.5 折 ~ 5 折</t>
+          <t>企业端/载体端</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>大客户额外折扣</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
+          <t>社区：AI 工具链≤1000万、行业垂类智能体≤1000万、Tokens券≤2000万、大厂团队≤1000万；企业：新质秀带创新券≤20万、首年房租物业全免、知产奖10万</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>2026.5.13 起施行，有效期一年</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="66" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>30 – 50 万</t>
+          <t>上海市 AI 赋能微短剧高质量发展若干措施</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>4 折 ~ 4.5 折</t>
+          <t>场景端</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>大客户额外折扣</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
+          <t>AI 微短剧智能体≤研发20%≤1000万；优秀微短剧≤300万（文商旅体展联动+50%）；优质厂牌≤200万；出海≤50万；课程≤20万；明确徐汇/杨浦/闵行建 AI 微短剧集聚区</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>2026.5.20 印发</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="66" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>50 – 100 万</t>
+          <t>上海市「模塑申城」工程补贴</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>3.5 折 ~ 4 折</t>
+          <t>企业端</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>大客户额外折扣</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
+          <t>算力券 / 模型券 / 语料券；适配 AIGC、AI 短剧、数字人、AI 营销、智能体、内容生成工具企业</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>2026 年度，每季度首月受理</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="66" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>100 – 300 万</t>
+          <t>上海市科技创新券</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>3 折 ~ 3.5 折</t>
+          <t>企业端</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>大客户额外折扣</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
+          <t>购买研发/转化/孵化/检测/科技金融/知产等服务可抵付；企业≤30万/年、团队≤10万/年，按≤50%兑付</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>2025.9.1–2030.8.31</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="66" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>300 – 500 万+</t>
+          <t>上海市创新产品市场化应用项目</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2.5 折 ~ 3 折</t>
+          <t>场景端</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>累计消费越多，折扣越低</t>
+          <t>研制单位 + 采购/承租单位联合申报，同一产品最多联合 5 家；贴合「5F 订单撮合」</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>以年度指南为准</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="66" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>上海市标志性重大应用场景 / 未来产业试验场</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>载体端/场景端</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>征集数字经济/AI 应用场景；对接场景贷、推荐创新产品目录；5F 可做「AI 数字内容高价值应用场景」背书</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>以年度指南为准</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="66" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>上海市消费新业态新模式新场景专项资金</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>企业端/场景端</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>跨界融合消费/AI+消费集聚区；补助≤项目审定投资30%；投资额≥100万；单企业周期内累计≤2000万</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>以年度指南为准</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
@@ -1810,137 +2808,154 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="74" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>05 · 招商漏斗 + 三年目标</t>
+          <t>04 · 后续摸排清单（政企联动落地）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>层级/项</t>
+          <t>摸排事项</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>名称</t>
+          <t>对接部门</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
+          <t>目的 / 判定</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>能否按创新创业载体/成果转化服务平台/场景清单申报</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>牌照锚定</t>
+          <t>区科经委</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>校友会/科企联/IP/玩具协会挂牌前置，客户「送进来」</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
+          <t>确立载体端政策兑现资格</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>3F 办公孵化 + 5F 展示交易能否作服务业引导资金项目</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>政策招商</t>
+          <t>区发改委</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>杨浦政策 + 火山引擎 + 算力补贴，作「入驻礼包」</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
+          <t>核算项目投资是否达 500 万门槛</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>取得 OPC 超级个体社区「认定条件」</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>社群/活动带流</t>
+          <t>区人民政府/科经委</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>OPC 社群、黑客松、小红书投流、漫展、沙龙、复旦科技园导流</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
+          <t>先决条件；未认定只能做协同/承接点</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>L4</t>
+          <t>杨浦 AI 微短剧集聚区承接空间；5F 可否作展示/路演/拍摄/协同点</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>资源转化</t>
+          <t>区文旅局</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>高校成果转化、IP 品牌方、链主配套、外贸玩具厂转化</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
+          <t>确立场景端承接身份</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>目标</t>
+          <t>建企业「算力/模型/语料」三券适配表</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>三年去化</t>
+          <t>市经信委/平台</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>首年 60% / 次年 70% / 第三年 85%（与基础运营费对赌）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
+          <t>核查算力合同、模型账单、语料合同、发票、日志</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>客群</t>
+          <t>科企联/服务机构是否入驻创新券平台</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>五类目标客户</t>
+          <t>科企联/服务机构</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>AI 项目 / 潮玩玩具文创 IP / 科技型中小 / 高校成果转化 / 生产性服务业</t>
+          <t>打通创新券在线下单、核验、兑付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>入驻企业产品进《创新产品推荐目录》→ 5F 找采购/承租联合申报</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>市经信委/采购方</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>落地 5F 订单撮合机制</t>
         </is>
       </c>
     </row>
@@ -1960,86 +2975,154 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="68" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>06 · 三年运营排期</t>
+          <t>04 · 火山引擎园区独立政策（优于火山工坊）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>阶段</t>
+          <t>累计消费区间</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>去化目标</t>
+          <t>额外折扣（代金券之外）</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>重点动作</t>
+          <t>说明</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>第 1 年 · 启动+导入</t>
+          <t>半年费用</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>无门槛免费</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>命名/招商手册/收费方案/政策汇编/首批挂牌/样板企业/首批招引 AI·IP·潮玩</t>
+          <t>按预估半年费用一次性发放代金券</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>第 2 年 · 成型+提质</t>
+          <t>0 – 10 万</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>5 折 ~ 7 折</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>重点客户补位/专精特新·高企培育/企业服务收费/漫展与沙龙常态化</t>
+          <t>大客户额外折扣</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>第 3 年 · 提升+复制</t>
+          <t>10 – 30 万</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>4.5 折 ~ 5 折</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>区级示范点/载体资质/补贴反哺/协同周边≤2项目/模式可复制</t>
+          <t>大客户额外折扣</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>30 – 50 万</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>4 折 ~ 4.5 折</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>大客户额外折扣</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>50 – 100 万</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>3.5 折 ~ 4 折</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>大客户额外折扣</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>100 – 300 万</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>3 折 ~ 3.5 折</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>大客户额外折扣</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>300 – 500 万+</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>2.5 折 ~ 3 折</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>累计消费越多，折扣越低</t>
         </is>
       </c>
     </row>
@@ -2059,245 +3142,143 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="74" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>07 · 合作报价总表 · 五类收费</t>
+          <t>05 · 招商漏斗 + 三年目标</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>收费项</t>
+          <t>层级/项</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>标准 / 口径</t>
+          <t>名称</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>支付方</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>说明</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>基础运营费</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>60 万/年（5 万/月）</t>
+          <t>牌照锚定</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>合作方按月</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>支持对赌，与去化目标挂钩</t>
+          <t>校友会/科企联/IP/玩具协会挂牌前置，客户「送进来」</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>对赌去化目标</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>首年 60% / 次年 70% / 第三年 85%</t>
+          <t>政策招商</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>达标机制，挂钩基础运营费</t>
+          <t>杨浦政策 + 火山引擎 + 算力补贴，作「入驻礼包」</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>人员配置</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>项目安排 2 人</t>
+          <t>社群/活动带流</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>含杨浦科技企业服务中心挂牌服务</t>
+          <t>OPC 社群、黑客松、小红书投流、漫展、沙龙、复旦科技园导流</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>招商佣金</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>成交后 2–3 个月租金（首年不重复计算）</t>
+          <t>资源转化</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>合作方</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>参照市场价</t>
+          <t>高校成果转化、IP 品牌方、链主配套、外贸玩具厂转化</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>挂牌费</t>
+          <t>目标</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>单个 3 万元，按数量与影响力分档</t>
+          <t>三年去化</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>合作方</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>国际会议厅费用另计</t>
+          <t>首年 60% / 次年 70% / 第三年 85%（与基础运营费对赌）</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>活动执行费</t>
+          <t>客群</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>每年约 30 场，打包 30 万元（每场≥30 人）</t>
+          <t>五类目标客户</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>合作方</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>含策划与执行</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>媒体流量费</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>每年 5 万元</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>合作方</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>详见「媒体报价」分表</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>企业增值服务</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>工商注册/政策申报/知识产权/税收法务/融资/出海撮合</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>入驻企业</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>成立联合公司经营分成</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>政府补贴与资质</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>协助申请相关政府补贴与企业资质</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>申请下的补贴归运营平台公司</t>
+          <t>AI 项目 / 潮玩玩具文创 IP / 科技型中小 / 高校成果转化 / 生产性服务业</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
@@ -2311,137 +3292,86 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="68" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>07 · 媒体报价（基础包 5 万/年）</t>
+          <t>06 · 三年运营排期</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>媒体项</t>
+          <t>阶段</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>内容</t>
+          <t>去化目标</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>计费方式</t>
+          <t>重点动作</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>小红书投流</t>
+          <t>第 1 年 · 启动+导入</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>话题/笔记投放，招募与引流</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>含基础包 / 超额按量</t>
+          <t>命名/招商手册/收费方案/政策汇编/首批挂牌/样板企业/首批招引 AI·IP·潮玩</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>账号代运营</t>
+          <t>第 2 年 · 成型+提质</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>园区及 IP 官方账号内容运营</t>
+          <t>70%</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>含基础包</t>
+          <t>重点客户补位/专精特新·高企培育/企业服务收费/漫展与沙龙常态化</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>短视频 / 直播间</t>
+          <t>第 3 年 · 提升+复制</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>活动直播、企业专访、产品发布</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>含基础包 / 专场另计</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>新闻通稿 / 软文</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>招商节点媒体声量</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>按篇 / 按节点</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>专项传播</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>漫展 / 峰会 / 挂牌等大型节点传播</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>按项目另计</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>基础包合计</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>上述常态化运营打包</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>5 万元/年</t>
+          <t>区级示范点/载体资质/补贴反哺/协同周边≤2项目/模式可复制</t>
         </is>
       </c>
     </row>

--- a/proposal/chuangzhihui-6600-proposal.xlsx
+++ b/proposal/chuangzhihui-6600-proposal.xlsx
@@ -23,7 +23,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09d 微短剧措施" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10 报价测算" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11 规划与拓展" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 风险应对" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11b 出海撮合模式" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11c 国际会客厅" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00 研判报告" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05b 招商运营计划" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05c 活动日历" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 风险应对" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -687,8 +692,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -721,7 +726,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>基础运营费</t>
@@ -729,7 +734,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>60 万/年（5 万/月）</t>
+          <t>96 万/年（8 万/月）</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -739,11 +744,11 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>支持对赌，与去化目标挂钩</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
+          <t>含 2 人在地团队，支持对赌</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
           <t>对赌去化目标</t>
@@ -751,7 +756,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>首年 60% / 次年 70% / 第三年 85%</t>
+          <t>三年平均 85%（或 首年 80% / 次年 85% / 第三年 95%）</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -765,7 +770,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>人员配置</t>
@@ -773,7 +778,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>项目安排 2 人</t>
+          <t>项目安排 2 人（招商 + 综合管理）</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -787,7 +792,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>招商佣金</t>
@@ -795,7 +800,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>成交后 2–3 个月租金（首年不重复计算）</t>
+          <t>成交后 1 个月租金（首年不重复计算）</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -805,11 +810,11 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>参照市场价</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
+          <t>按进价/净值计（市场为 2–3 月）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>挂牌费</t>
@@ -831,7 +836,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
           <t>活动执行费</t>
@@ -849,11 +854,11 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>含策划与执行</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
+          <t>含策划、执行、导师及物料</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
           <t>媒体流量费</t>
@@ -861,7 +866,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>每年 5 万元</t>
+          <t>每年 10 万元（含网络投流）</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -871,11 +876,11 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>详见「媒体报价」分表</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
+          <t>官媒背书 5 万 + 自媒体/投流 5 万</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
           <t>企业增值服务</t>
@@ -897,7 +902,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
           <t>政府补贴与资质</t>
@@ -1591,7 +1596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1623,7 +1628,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1">
+    <row r="3" ht="36" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>固定服务包(年)</t>
@@ -1631,16 +1636,16 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>约 95 万/年</t>
+          <t>约 136 万/年</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>基础运营 60 万 + 活动 30 万 + 媒体 5 万</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
+          <t>基础运营 96 万 + 活动 30 万 + 媒体 10 万</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
           <t>招商佣金(浮动)</t>
@@ -1648,16 +1653,16 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>成交后 2–3 个月租金</t>
+          <t>成交后 1 个月租金</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>首年不重复计算</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
+          <t>首年不重复；按进价/净值计</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>挂牌费(浮动)</t>
@@ -1674,7 +1679,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1">
+    <row r="6" ht="36" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>增值服务(浮动)</t>
@@ -1687,82 +1692,99 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>工商/政策/知产/财税法务/融资/出海</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
+          <t>工商/政策/知产/财税法务/融资/出海撮合</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
+          <t>出海撮合(浮动)</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>平台利润 1–30 万/项目；落地佣金 1%–3%</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>展厅订单扣点反哺租金，超额进合资公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
           <t>补贴归属</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>归运营平台公司</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>协助申请，成功兑现为准</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>——对方测算——</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr"/>
-      <c r="C8" s="6" t="inlineStr"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr"/>
+      <c r="C9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>对方空间成本</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>≈554 万/年</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>2.3 元/㎡/天 × 6600㎡ × 365</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>我方固定服务包</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>约 95 万/年 + 佣金</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>由对方利润/中建四局运营费列支，非纯增量</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>约 136 万/年 + 佣金</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>由对方利润/合作方运营费列支，非纯增量</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>对方收益</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>去化率 60→70→85%、企业质量↑、政策承接、品牌示范</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>去化 80→85→95%（均85%）、企业质量↑、政策承接、出海故事</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>比照元谷「花一份钱赚四份钱」逻辑</t>
         </is>
@@ -1898,89 +1920,512 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="74" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="82" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>风险点与应对</t>
+          <t>08 · 出海撮合业务 · 合作模式与收入</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>风险</t>
+          <t>环节 / 项</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>应对</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="34" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>空间合规（用途/消防/承重/用电）</t>
+          <t>展厅免租机制</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>入驻准入审核；以轻型研发/中试/装配/测试与办公展示为主，拒高污染高噪音高能耗</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
+          <t>5F 展厅对优质企业免租，约定租金标准 + 物业费</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>招商去化</t>
+          <t>订单扣点反哺</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>先样板企业 + 首批优惠 + 高校/协会/社群/复旦科技园渠道 + 政策抓手；对赌 60/70/85%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
+          <t>出海达成订单后按扣点反哺租金</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>收益周期</t>
+          <t>超额分成</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>基础运营费保障；佣金与去化挂钩；增值服务逐步导入，避免前期重投入</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
+          <t>超出租金部分进入合资公司收益</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>政策兑现</t>
+          <t>合资分配</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>一切以政府最新文件为准；不承诺必得补贴；服务以辅导/申报/对接为主，成功费按实际兑现计</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
+          <t>运营平台方与合作方按约定分配（平台方约占 30%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>合作复制边界</t>
+          <t>平台利润</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>协同周边 ≤2 个项目；单项目单核算，避免人力成本覆盖不住</t>
+          <t>出海撮合单项目 1–30 万</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>落地佣金</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>项目额 1%–3%（按行业浮动；建筑类大额项目抽点低）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>产业撮合会员</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>搭一级协会组织，年度顾问 / 游学 / 高级专家，形成粘性</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>行业聚焦</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>供应链（玩具/毛绒/潮玩 OEM→品牌）+ 内容（AI 短剧/IP 授权）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>对接层级</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>连领事 → 对接所在国商务部/部长 → 业务洽谈 → 落地</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>团队</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>初期各部门抽调兼职（1 人起），成熟设全职约 3 人，单独成立公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>沪穗联动</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>与广州自贸港/电商出海项目协同，两地共享资源</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>08 · 国际会议厅 · 国家会客厅（收入示意）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>产品 / 项</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>价格区间</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>国家独家冠名</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>80–300 万/年</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>国别命名、领事资源优先、招商对接</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>联合冠名</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>30–80 万</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>主题季/联合命名、活动优先、品牌权益</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>企业常驻会籍</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>10–30 万/年</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>常驻席位、出海与对接优先、活动权益</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>单场地 + 领事出席</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>3–10 万/次</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>场地、领事/政要出席、文化体验</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>园区·政府招商包</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>30–100 万/项目</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>外资项目对接、国别窗口、落地协助</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>出海单国服务包</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>20–50 万/项目</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>连领事 → 对接部长 → 落地陪跑</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>出海年度顾问</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>50–150 万/年</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>全年陪跑顾问</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>落地成功佣金</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>项目额 1%–5%</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>成交分成</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>三方分润</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>领事合作方 40–50% / 企联 25–35% / 复旦 15–25%</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>按项目类型浮动；合作方名称保密处理</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="84" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>00 · 项目研判报告（要点）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>维度</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>研判要点</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>区位研判</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>五角场城市副中心 + 环同济；创智天地正处 YOUNG立方内容集聚区核心圈</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>市场研判</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>AI+ 与数字内容政策红利期；微短剧/AIGC/数字人爆发；沪建 AI 微短剧集聚区（徐汇·杨浦·闵行）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>政策研判</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>市区两级政策叠加；载体认定 + 三券 + 补贴形成兑现能力</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>客群研判</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>AI 应用/AIGC/数字人、AI 短剧、数字 IP、创意设计、智能营销、OPC；供应链与内容 IP 出海</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>S 优势</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>政策核心圈 + 环同济 + 高校大厂 + AI/OPC 社群 + IP/领事/出海资源 + 离运营方近</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>W 劣势</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>体量小；载体/OPC 社区等认定待落实；出海撮合需自有资源与专职团队</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>O 机会</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>微短剧/AIGC 红利、出海撮合 + 国家会客厅高毛利、沪穗联动可复制</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>T 威胁</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>去化对赌压力（三年均 85%）；政策兑现不确定；跨行业撮合难</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>研判结论</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>需求真实、政策强、区位优——具备「政策引导产业落位 + 出海撮合放大」的稀缺条件</t>
         </is>
       </c>
     </row>
@@ -2202,6 +2647,442 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="88" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>05 · 招商运营策划及计划方案</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>板块</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>要点</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="34" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>招商打法</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>牌照锚定 + 政策礼包前置；小红书投流→线下 AI 培训→转化；复旦科技园+高校大厂+IP/协会导流</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>运营团队</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>在地 2 人（招商 + 综合管理）；出海撮合初期兼职、成熟全职约 3 人；挂牌科企服务中心</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>运营节奏</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>月度招商目标 + 去化看板（对赌三年均 85%）；常态化活动完成载体 KPI，运营满年申请补贴（约一二十万）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>0–3 月</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>定位包装 + 政策梳理 + 首批挂牌 + 样板企业</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>3–6 月</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>集中招引 + 首批优惠 + 推介路演 + 政策诊断</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>6–12 月</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>重点补位 + 专精特新/高企培育 + 首场漫展</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>全周期</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>活动 IP 化 + 出海撮合 + 补贴反哺 + 协同复制</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>05 · 活动安排计划 · 年度活动日历（约 30 场）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>频次/年</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>作用</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>AI 培训 / 黑客松</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>约 10 场</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>OPC 社群、AI 工具链、AIGC 实操</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>引流转化 → 租客</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>政策沙龙 / 路演</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>约 6 场</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>政策解读、专精特新/高企培育、投融资</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>政策兑现 + 招商</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>行业对接 / 撮合</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>约 6 场</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>供应链/IP 出海对接、产业撮合、游学</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>出海撮合 + 会员粘性</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>IP / 潮玩活动</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>约 4 场</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>IP 首发、主题市集、沉浸式展览</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>5F 引流 + 商业变现</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>漫展 / 大型活动</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>约 2 场</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>千人级漫展（门票+赞助）、峰会借势</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>声量 + 经营性收入</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>领事专题 / 出海活动</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>约 2 场</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>国家会客厅领事专题、出海推介</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>高端背书 + 出海</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>约 30 场</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>对标魔术空间约 110 场/年，30 场为基线</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>招商 + 载体 KPI + 补贴</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="74" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>风险点与应对</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>风险</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>应对</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>空间合规（用途/消防/承重/用电）</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>入驻准入审核；以轻型研发/中试/装配/测试与办公展示为主，拒高污染高噪音高能耗</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>招商去化</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>先样板企业 + 首批优惠 + 高校/协会/社群/复旦科技园渠道 + 政策抓手；对赌 60/70/85%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>收益周期</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>基础运营费保障；佣金与去化挂钩；增值服务逐步导入，避免前期重投入</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>政策兑现</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>一切以政府最新文件为准；不承诺必得补贴；服务以辅导/申报/对接为主，成功费按实际兑现计</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>合作复制边界</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>协同周边 ≤2 个项目；单项目单核算，避免人力成本覆盖不住</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -3292,7 +4173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3332,7 +4213,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -3349,7 +4230,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -3366,12 +4247,29 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>区级示范点/载体资质/补贴反哺/协同周边≤2项目/模式可复制</t>
+          <t>区级示范点/载体资质/补贴反哺/出海撮合放量/协同周边≤2项目</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>三年平均</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>≥85%</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>对赌口径：三年平均 85%（或 首年80%/次年85%/三年95%）</t>
         </is>
       </c>
     </row>

--- a/proposal/chuangzhihui-6600-proposal.xlsx
+++ b/proposal/chuangzhihui-6600-proposal.xlsx
@@ -28,7 +28,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00 研判报告" sheetId="19" state="visible" r:id="rId19"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05b 招商运营计划" sheetId="20" state="visible" r:id="rId20"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05c 活动日历" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 风险应对" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11d 营收-收入结构" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11e 营收-成本盈亏" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 风险应对" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2987,6 +2989,425 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>08 · 营收逻辑 · 收入结构（3F+5F 整体，示意）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>口径 / 类别</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>科目</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>年化（示意）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>园区空间盘（甲方）</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>3F 办公租金 2850㎡</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>约 400 万（85% 去化 · ~4.5 元/㎡/天）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>园区空间盘（甲方）</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>5F 展贸租金 + 物业</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>约 300 万（部分免租 · 订单扣点反哺）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>园区空间盘（甲方）</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>6600㎡ 物业费</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>约 200 万（1.0 元/㎡/天 计）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>园区空间盘（甲方）</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>空间盘合计</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>约 900 万/年（满租稳定期）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>运营平台（乙方）</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>固定服务费</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>约 146 万（运营 96 + 活动 30 + 媒体 10 + 挂牌）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>运营平台（乙方）</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>招商佣金</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>1 月租金/成交（约 30–50 万）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>运营平台（乙方）</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>增值 + 出海分成</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>约 150–450 万（联合公司）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>运营平台（乙方）</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>经营性 + 补贴</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>约 50–100 万（门票/培训/空间 + 载体奖励）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>运营平台（乙方）</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>平台收入合计</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>约 380–740 万/年（稳定期示意区间）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="56" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>08 · 营收逻辑 · 成本结构与盈亏测算（示意）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>项目</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>口径 / 金额</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>团队人力</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>100–180 万/年</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>在地 2 + 出海 1–3 + 兼职</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>活动执行</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>约 30 万/年</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>约 30 场，含导师与物料</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>媒体 + 网络投流</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>约 10 万/年</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>官媒 5 + 自媒体/投流 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>运营杂费/差旅/办公</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>20–40 万/年</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>日常运营</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>硬件装修摊销</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>甲方为主</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>乙方轻资产，前期投入低</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>成本合计</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>约 160–260 万/年</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>运营平台口径</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>情景·保守</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>净 +195 万</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>收入 ~380 万 − 成本 ~185 万</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>情景·中性</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>净 +300 万</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>收入 ~520 万 − 成本 ~220 万</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>情景·乐观</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>净 +480 万</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>收入 ~740 万 − 成本 ~260 万</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>盈亏与现金流</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>保底 96 万/年</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>三情景净收益均为正；出海撮合为最大增长弹性</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/proposal/chuangzhihui-6600-proposal.xlsx
+++ b/proposal/chuangzhihui-6600-proposal.xlsx
@@ -28,9 +28,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00 研判报告" sheetId="19" state="visible" r:id="rId19"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05b 招商运营计划" sheetId="20" state="visible" r:id="rId20"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05c 活动日历" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11d 营收-收入结构" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11e 营收-成本盈亏" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 风险应对" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11f 大湾区出海资源" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11g 战略资源探讨" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11d 营收-收入结构" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11e 营收-成本盈亏" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 风险应对" sheetId="26" state="visible" r:id="rId26"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -731,78 +733,78 @@
     <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>基础运营费</t>
+          <t>招商佣金（强化）</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>96 万/年（8 万/月）</t>
+          <t>成交后 2–3 个月租金（首年不重复）</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>合作方按月</t>
+          <t>合作方</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>含 2 人在地团队，支持对赌</t>
+          <t>市场标准，招商板块主收费；招商不对赌</t>
         </is>
       </c>
     </row>
     <row r="4" ht="40" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>对赌去化目标</t>
+          <t>活动执行费</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>三年平均 85%（或 首年 80% / 次年 85% / 第三年 95%）</t>
+          <t>每年约 30 场，打包 30 万元（每场≥30 人）</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>合作方</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>达标机制，挂钩基础运营费</t>
+          <t>含策划、执行、导师及物料</t>
         </is>
       </c>
     </row>
     <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>人员配置</t>
+          <t>挂牌费</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>项目安排 2 人（招商 + 综合管理）</t>
+          <t>单个 3 万元，按数量与影响力分档</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>合作方</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>含杨浦科技企业服务中心挂牌服务</t>
+          <t>国际会议厅费用另计</t>
         </is>
       </c>
     </row>
     <row r="6" ht="40" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>招商佣金</t>
+          <t>媒体流量费</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>成交后 1 个月租金（首年不重复计算）</t>
+          <t>每年 10 万元（含网络投流）</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -812,107 +814,107 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>按进价/净值计（市场为 2–3 月）</t>
+          <t>官媒背书 5 万 + 自媒体/投流 5 万</t>
         </is>
       </c>
     </row>
     <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>挂牌费</t>
+          <t>出海专项服务费</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>单个 3 万元，按数量与影响力分档</t>
+          <t>出海协议框架内计收（由原月费转化，非月费）</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>合作方</t>
+          <t>合作方/合资公司</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>国际会议厅费用另计</t>
+          <t>含 2–3 人出海团队，强化国际出海职能</t>
         </is>
       </c>
     </row>
     <row r="8" ht="40" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>活动执行费</t>
+          <t>出海撮合佣金</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>每年约 30 场，打包 30 万元（每场≥30 人）</t>
+          <t>平台利润 1–30 万/项目 + 落地佣金 1%–3%</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>合作方</t>
+          <t>合资公司</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>含策划、执行、导师及物料</t>
+          <t>国际出海收费重点</t>
         </is>
       </c>
     </row>
     <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>媒体流量费</t>
+          <t>企业增值服务</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>每年 10 万元（含网络投流）</t>
+          <t>工商注册/政策申报/知识产权/税收法务/融资/出海撮合</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>合作方</t>
+          <t>入驻企业</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>官媒背书 5 万 + 自媒体/投流 5 万</t>
+          <t>成立联合公司经营分成</t>
         </is>
       </c>
     </row>
     <row r="10" ht="40" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>企业增值服务</t>
+          <t>政府补贴与资质</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>工商注册/政策申报/知识产权/税收法务/融资/出海撮合</t>
+          <t>协助申请相关政府补贴与企业资质</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>入驻企业</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>成立联合公司经营分成</t>
+          <t>申请下的补贴归运营平台公司</t>
         </is>
       </c>
     </row>
     <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>政府补贴与资质</t>
+          <t>合作方式说明</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>协助申请相关政府补贴与企业资质</t>
+          <t>招商轻资产·不对赌；月费转化为出海专项服务费</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -922,7 +924,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>申请下的补贴归运营平台公司</t>
+          <t>双协议：招商轻运营 + 出海联合运营</t>
         </is>
       </c>
     </row>
@@ -1633,34 +1635,34 @@
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>固定服务包(年)</t>
+          <t>招商佣金(强化)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>约 136 万/年</t>
+          <t>成交后 2–3 个月租金</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>基础运营 96 万 + 活动 30 万 + 媒体 10 万</t>
+          <t>首年不重复；招商板块主收费</t>
         </is>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>招商佣金(浮动)</t>
+          <t>活动 + 媒体</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>成交后 1 个月租金</t>
+          <t>活动 30 万 + 媒体 10 万（含投流）</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>首年不重复；按进价/净值计</t>
+          <t>含策划执行、导师物料；官媒5+自媒体投流5</t>
         </is>
       </c>
     </row>
@@ -1684,17 +1686,17 @@
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>增值服务(浮动)</t>
+          <t>出海专项服务费</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>联合公司经营分成</t>
+          <t>由原月费转化，出海协议内计收</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>工商/政策/知产/财税法务/融资/出海撮合</t>
+          <t>含 2–3 人出海团队，强化国际出海职能</t>
         </is>
       </c>
     </row>
@@ -1718,77 +1720,77 @@
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>补贴归属</t>
+          <t>增值服务(浮动)</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>归运营平台公司</t>
+          <t>联合公司经营分成</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>协助申请，成功兑现为准</t>
+          <t>工商/政策/知产/财税法务/融资/出海撮合</t>
         </is>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>——对方测算——</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr"/>
-      <c r="C9" s="4" t="inlineStr"/>
+          <t>补贴归属</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>归运营平台公司</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>协助申请，成功兑现为准</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>对方空间成本</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>≈554 万/年</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>2.3 元/㎡/天 × 6600㎡ × 365</t>
-        </is>
-      </c>
+          <t>——对方测算——</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr"/>
+      <c r="C10" s="6" t="inlineStr"/>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>我方固定服务包</t>
+          <t>对方空间成本</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>约 136 万/年 + 佣金</t>
+          <t>≈554 万/年</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>由对方利润/合作方运营费列支，非纯增量</t>
+          <t>2.3 元/㎡/天 × 6600㎡ × 365</t>
         </is>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>对方收益</t>
+          <t>合作方式</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>去化 80→85→95%（均85%）、企业质量↑、政策承接、出海故事</t>
+          <t>招商轻资产·不对赌；出海重收费</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>比照元谷「花一份钱赚四份钱」逻辑</t>
+          <t>月费转出海专项服务费；佣金强化 2–3 月</t>
         </is>
       </c>
     </row>
@@ -2989,6 +2991,337 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="78" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>08 · 大湾区出海资源叠加（复旦系 + 高校，沪穗联动）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>资源</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>能力 / 说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="38" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>复旦珠海创新研究院</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>九大公共平台（集成电路/大数据智算/工业仿真/海洋科技/物联网智慧城市/先进材料）；手心研发·手背转化；服务横琴粤澳深合区</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="38" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>中国—葡语国家科技合作平台</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>横琴对接葡语系（巴西/葡萄牙/安哥拉/莫桑比克）唯一国家级平台；市场调研·本地匹配·海外展会·合规咨询</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="38" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>珠澳双循环出海窗口</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>澳门自由港 + 葡语商贸平台；内地研发+澳门展销+葡语国家落地；海外总部/海外仓中转，规避关税壁垒</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="38" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>海洋科技/物联网海外转化</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>海洋监测/智慧城市物联网经横琴出口东南亚、拉美沿海；海外项目联合申报、海外工程落地</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="38" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>复旦广州校友会</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>广州本地校友网络与资源对接</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="38" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>粤港澳大湾区精准医学研究院</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>省市南沙复旦联和健康五方共建；南沙唯一万笼级实验动物中心；肿瘤/代谢/生殖精准诊疗、类器官、医疗器械转化</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="38" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>深圳复旦研究院</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>河套深港科创合作区；AI/前沿医学/集成电路；联动香港，打通深港产学研</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="38" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>粤港澳复旦科技成果转化服务中心</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>复旦技术转移落地南沙；技术授权海外/海外联合研发/国际专利；对接新加坡·英·美医学机构；海外临床申报与国际认证</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="38" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>港澳跨境协同通道</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>联动香港生物医药创新协会/香港科技园；海外样品通关·市场准入·投融资路演；长三角-大湾区-海外对接会</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="38" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>出海基金矩阵</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>粤科复旦母基金、南沙科创产业基金；海外建厂/分销/研发中心；跨境股权融资、跨境担保</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="38" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>暨南大学 / 华侨大学</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>侨校资源，服务东南亚等海外华人华侨市场</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="38" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>广东外语外贸大学</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>出海第一梯队：小语种（东盟/葡语/西语）·海丝国别智库·跨境合规·国际贸易·海外市场调研</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="38" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>广州大学黄埔研究院</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>数字经济·跨境新媒体·海外独立站·智能制造国际转化</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>08 · 战略资源探讨（东方枢纽/谷歌/领英，待落实）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>资源</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>探讨方向</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>在项目中的作用</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>东方枢纽</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>国际商务合作区 + 综保区 + 空铁枢纽</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>出海企业境内关外通道、保税展示、国际中转与海外仓承接点</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>谷歌 Google</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Google Ads / YouTube 出海投放；谷歌在领事馆/国别活动中的技术与流量角色</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>叠加海外数字营销通路，服务内容与货品出海</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>领英 LinkedIn</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>B2B 海外决策人触达、品牌出海、海外招募</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>国际出海职能线上主通路之一，与展会/领事撮合互补</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>收费落点</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>出海专项服务费 + 撮合佣金 + 海外营销投放代运营 + 国家会客厅冠名/会籍</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>强化国际出海职能并在出海板块收费</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>东方枢纽与谷歌合作以实际对接结果为准</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>本页为探讨方向，不构成承诺</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3184,7 +3517,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3402,7 +3735,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4634,7 +4967,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>参考 80%</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -4651,12 +4984,12 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>参考 85%</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>重点客户补位/专精特新·高企培育/企业服务收费/漫展与沙龙常态化</t>
+          <t>重点客户补位/专精特新·高企培育/企业服务收费/出海撮合起量</t>
         </is>
       </c>
     </row>
@@ -4668,7 +5001,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>参考 95%</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -4680,17 +5013,17 @@
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>三年平均</t>
+          <t>去化口径</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>≥85%</t>
+          <t>参考·不对赌</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>对赌口径：三年平均 85%（或 首年80%/次年85%/三年95%）</t>
+          <t>招商板块轻资产、不对赌；去化为参考目标（原对赌已取消）</t>
         </is>
       </c>
     </row>

--- a/proposal/chuangzhihui-6600-proposal.xlsx
+++ b/proposal/chuangzhihui-6600-proposal.xlsx
@@ -28,11 +28,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00 研判报告" sheetId="19" state="visible" r:id="rId19"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05b 招商运营计划" sheetId="20" state="visible" r:id="rId20"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05c 活动日历" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11f 大湾区出海资源" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11g 战略资源探讨" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11d 营收-收入结构" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11e 营收-成本盈亏" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 风险应对" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10b 政策申报收入" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10c 会客厅测算" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10d 企业服务测算" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11f 大湾区出海资源" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11g 战略资源探讨" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11d 营收-收入结构" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11e 营收-成本盈亏" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 风险应对" sheetId="29" state="visible" r:id="rId29"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2991,191 +2994,245 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="78" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>08 · 大湾区出海资源叠加（复旦系 + 高校，沪穗联动）</t>
+          <t>08 · 财务测算 · 政策申报收入（能否拿到现金）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>资源</t>
+          <t>政策</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>能力 / 说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="38" customHeight="1">
+          <t>金额（含单位）</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>平台可实现现金（单位）</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>现金确定性</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>复旦珠海创新研究院</t>
+          <t>载体运营/活动补贴（科技服务业·成果转化平台）</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>九大公共平台（集成电路/大数据智算/工业仿真/海洋科技/物联网智慧城市/先进材料）；手心研发·手背转化；服务横琴粤澳深合区</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="38" customHeight="1">
+          <t>认定后≤100 万/年；运营满年约 10–20 万/年</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>直接到平台 10–20 万/年</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>现金·较确定（认定+满年）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>中国—葡语国家科技合作平台</t>
+          <t>高新技术企业认定</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>横琴对接葡语系（巴西/葡萄牙/安哥拉/莫桑比克）唯一国家级平台；市场调研·本地匹配·海外展会·合规咨询</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="38" customHeight="1">
+          <t>首次 20 万/次（企业·一次性）</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>申报服务费 2–8 万/家</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>现金·确定（服务费）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>珠澳双循环出海窗口</t>
+          <t>专精特新</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>澳门自由港 + 葡语商贸平台；内地研发+澳门展销+葡语国家落地；海外总部/海外仓中转，规避关税壁垒</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="38" customHeight="1">
+          <t>市级 10 / 国家小巨人 30 万（企业·一次性）</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>服务费 2–8 万/家</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>现金·确定（服务费）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>海洋科技/物联网海外转化</t>
+          <t>科技型中小企业备案</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>海洋监测/智慧城市物联网经横琴出口东南亚、拉美沿海；海外项目联合申报、海外工程落地</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="38" customHeight="1">
+          <t>资格（企业·无直接现金）</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>服务费 0.3–2 万/家</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>现金·确定（服务费）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>复旦广州校友会</t>
+          <t>AI/大数据房租补贴</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>广州本地校友网络与资源对接</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="38" customHeight="1">
+          <t>2 元/天/㎡·≤100 万/年（企业·3 年）</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>代申请成功费 到账 5%–15%</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>现金·依到账</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>粤港澳大湾区精准医学研究院</t>
+          <t>政府补贴项目（各类）</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>省市南沙复旦联和健康五方共建；南沙唯一万笼级实验动物中心；肿瘤/代谢/生殖精准诊疗、类器官、医疗器械转化</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="38" customHeight="1">
+          <t>视项目（企业）</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>成功费 到账额 5%–15%</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>现金·以兑现为准</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>深圳复旦研究院</t>
+          <t>科技创新券</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>河套深港科创合作区；AI/前沿医学/集成电路；联动香港，打通深港产学研</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="38" customHeight="1">
+          <t>企业≤30 万·团队≤10 万/年（抵付服务）</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>作服务机构核销分成</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>现金·需入驻创新券平台</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>粤港澳复旦科技成果转化服务中心</t>
+          <t>算力补贴 + 云折扣</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>复旦技术转移落地南沙；技术授权海外/海外联合研发/国际专利；对接新加坡·英·美医学机构；海外临床申报与国际认证</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="38" customHeight="1">
+          <t>最高 50%（企业）</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>招商抓手（非平台现金）</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>非现金（招商用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>港澳跨境协同通道</t>
+          <t>未来预判</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>联动香港生物医药创新协会/香港科技园；海外样品通关·市场准入·投融资路演；长三角-大湾区-海外对接会</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="38" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>出海基金矩阵</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>粤科复旦母基金、南沙科创产业基金；海外建厂/分销/研发中心；跨境股权融资、跨境担保</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="38" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>暨南大学 / 华侨大学</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>侨校资源，服务东南亚等海外华人华侨市场</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="38" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>广东外语外贸大学</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>出海第一梯队：小语种（东盟/葡语/西语）·海丝国别智库·跨境合规·国际贸易·海外市场调研</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="38" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>广州大学黄埔研究院</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>数字经济·跨境新媒体·海外独立站·智能制造国际转化</t>
+          <t>微短剧专项 / 模塑申城三券 / YOUNG立方直播券·活动补贴</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>窗口开放后追加</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>待窗口</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
@@ -3189,120 +3246,222 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>08 · 战略资源探讨（东方枢纽/谷歌/领英，待落实）</t>
+          <t>08 · 财务测算 · 国际会客厅（北欧会客厅）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>资源</t>
+          <t>类别</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>探讨方向</t>
+          <t>项目</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>在项目中的作用</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="40" customHeight="1">
+          <t>金额（含单位）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="34" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>东方枢纽</t>
+          <t>合作模式</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>国际商务合作区 + 综保区 + 空铁枢纽</t>
+          <t>一段话</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>出海企业境内关外通道、保税展示、国际中转与海外仓承接点</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="40" customHeight="1">
+          <t>联合领事资源合作方，以「北欧/国别会客厅」为载体做外事接待·文化展示·招商对接·企业出海；平台运营策划+活动+撮合，按冠名/会籍/活动/出海对接收费并分润</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>谷歌 Google</t>
+          <t>收费</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Google Ads / YouTube 出海投放；谷歌在领事馆/国别活动中的技术与流量角色</t>
+          <t>冠名/联合冠名</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>叠加海外数字营销通路，服务内容与货品出海</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="40" customHeight="1">
+          <t>30–80 万/年</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>领英 LinkedIn</t>
+          <t>收费</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>B2B 海外决策人触达、品牌出海、海外招募</t>
+          <t>企业会籍</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>国际出海职能线上主通路之一，与展会/领事撮合互补</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="40" customHeight="1">
+          <t>10 万/家/年（保守 3–5 家）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>收费落点</t>
+          <t>收费</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>出海专项服务费 + 撮合佣金 + 海外营销投放代运营 + 国家会客厅冠名/会籍</t>
+          <t>单场活动（领事出席）</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>强化国际出海职能并在出海板块收费</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="40" customHeight="1">
+          <t>3–8 万/场（6–8 场/年）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>说明</t>
+          <t>收费</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>东方枢纽与谷歌合作以实际对接结果为准</t>
+          <t>出海对接服务</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>本页为探讨方向，不构成承诺</t>
+          <t>单国服务包 20–50 万/项目</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>成本</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>活动执行</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>3–5 万/场</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>成本</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>领事/嘉宾对接接待</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>2–5 万/场</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>成本</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>空间/场地分摊</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>按次或年（合作方空间）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>成本</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>合作方分润</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>领事资源方 40%–50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>合理预估</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>首年</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>收入 ~80–120 万，平台净 ~20–40 万/年</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>合理预估</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>成熟期</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>收入 ~150–250 万，平台净 ~50–90 万/年（不高估，待确认）</t>
         </is>
       </c>
     </row>
@@ -3325,185 +3484,185 @@
   <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>08 · 营收逻辑 · 收入结构（3F+5F 整体，示意）</t>
+          <t>08 · 财务测算 · 企业服务（项目/收费/成本）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>口径 / 类别</t>
+          <t>服务项目</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>科目</t>
+          <t>收费（含单位）</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>年化（示意）</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
+          <t>成本（含单位）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>园区空间盘（甲方）</t>
+          <t>工商注册 · 代账</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>3F 办公租金 2850㎡</t>
+          <t>注册引流免费；代账 3000–6000 元/年/家</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>约 400 万（85% 去化 · ~4.5 元/㎡/天）</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
+          <t>第三方分成 + 人力</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>园区空间盘（甲方）</t>
+          <t>政策申报</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>5F 展贸租金 + 物业</t>
+          <t>普通 0.3–2 万/项；高企/专精特新 2–8 万/项；补贴成功费 到账 5%–15%</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>约 300 万（部分免租 · 订单扣点反哺）</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="32" customHeight="1">
+          <t>人力 + 材料杂费</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>园区空间盘（甲方）</t>
+          <t>知识产权</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>6600㎡ 物业费</t>
+          <t>商标 800–2000 元/件；软著 2000–5000 元/件；专利代理 5000–1 万/件</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>约 200 万（1.0 元/㎡/天 计）</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1">
+          <t>第三方分成</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>园区空间盘（甲方）</t>
+          <t>财税 · 法务</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>空间盘合计</t>
+          <t>顾问 1–5 万/年/家</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>约 900 万/年（满租稳定期）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
+          <t>第三方分成</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>运营平台（乙方）</t>
+          <t>融资顾问</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>固定服务费</t>
+          <t>成功佣金 融资额 1%–3%</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>约 146 万（运营 96 + 活动 30 + 媒体 10 + 挂牌）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="32" customHeight="1">
+          <t>人力</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>运营平台（乙方）</t>
+          <t>出海撮合</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>招商佣金</t>
+          <t>平台利润 1–30 万/项目 + 落地佣金 1%–3%</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>1 月租金/成交（约 30–50 万）</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="32" customHeight="1">
+          <t>出海团队（单列）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>运营平台（乙方）</t>
+          <t>人力成本（必列示）</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>增值 + 出海分成</t>
+          <t>企业服务暂不设专职，按兼职/共享列示</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>约 150–450 万（联合公司）</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="32" customHeight="1">
+          <t>约 15–30 万/年（社保+人力）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>运营平台（乙方）</t>
+          <t>第三方分成 / 杂费</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>经营性 + 补贴</t>
+          <t>第三方服务分成 按收入 30%–50%</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>约 50–100 万（门票/培训/空间 + 载体奖励）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1">
+          <t>系统/材料杂费 约 2–5 万/年</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>运营平台（乙方）</t>
+          <t>合理预估</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>平台收入合计</t>
+          <t>首年企业服务收入(不含出海) ~30–60 万</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>约 380–740 万/年（稳定期示意区间）</t>
+          <t>净利 ~10–25 万</t>
         </is>
       </c>
     </row>
@@ -3523,6 +3682,538 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="78" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>08 · 大湾区出海资源叠加（复旦系 + 高校，沪穗联动）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>资源</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>能力 / 说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="38" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>复旦珠海创新研究院</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>九大公共平台（集成电路/大数据智算/工业仿真/海洋科技/物联网智慧城市/先进材料）；手心研发·手背转化；服务横琴粤澳深合区</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="38" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>中国—葡语国家科技合作平台</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>横琴对接葡语系（巴西/葡萄牙/安哥拉/莫桑比克）唯一国家级平台；市场调研·本地匹配·海外展会·合规咨询</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="38" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>珠澳双循环出海窗口</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>澳门自由港 + 葡语商贸平台；内地研发+澳门展销+葡语国家落地；海外总部/海外仓中转，规避关税壁垒</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="38" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>海洋科技/物联网海外转化</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>海洋监测/智慧城市物联网经横琴出口东南亚、拉美沿海；海外项目联合申报、海外工程落地</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="38" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>复旦广州校友会</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>广州本地校友网络与资源对接</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="38" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>粤港澳大湾区精准医学研究院</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>省市南沙复旦联和健康五方共建；南沙唯一万笼级实验动物中心；肿瘤/代谢/生殖精准诊疗、类器官、医疗器械转化</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="38" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>深圳复旦研究院</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>河套深港科创合作区；AI/前沿医学/集成电路；联动香港，打通深港产学研</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="38" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>粤港澳复旦科技成果转化服务中心</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>复旦技术转移落地南沙；技术授权海外/海外联合研发/国际专利；对接新加坡·英·美医学机构；海外临床申报与国际认证</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="38" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>港澳跨境协同通道</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>联动香港生物医药创新协会/香港科技园；海外样品通关·市场准入·投融资路演；长三角-大湾区-海外对接会</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="38" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>出海基金矩阵</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>粤科复旦母基金、南沙科创产业基金；海外建厂/分销/研发中心；跨境股权融资、跨境担保</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="38" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>暨南大学 / 华侨大学</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>侨校资源，服务东南亚等海外华人华侨市场</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="38" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>广东外语外贸大学</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>出海第一梯队：小语种（东盟/葡语/西语）·海丝国别智库·跨境合规·国际贸易·海外市场调研</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="38" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>广州大学黄埔研究院</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>数字经济·跨境新媒体·海外独立站·智能制造国际转化</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>08 · 战略资源探讨（东方枢纽/谷歌/领英，待落实）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>资源</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>探讨方向</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>在项目中的作用</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>东方枢纽</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>国际商务合作区 + 综保区 + 空铁枢纽</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>出海企业境内关外通道、保税展示、国际中转与海外仓承接点</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>谷歌 Google</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Google Ads / YouTube 出海投放；谷歌在领事馆/国别活动中的技术与流量角色</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>叠加海外数字营销通路，服务内容与货品出海</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>领英 LinkedIn</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>B2B 海外决策人触达、品牌出海、海外招募</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>国际出海职能线上主通路之一，与展会/领事撮合互补</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>收费落点</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>出海专项服务费 + 撮合佣金 + 海外营销投放代运营 + 国家会客厅冠名/会籍</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>强化国际出海职能并在出海板块收费</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>东方枢纽与谷歌合作以实际对接结果为准</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>本页为探讨方向，不构成承诺</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>08 · 营收逻辑 · 收入结构（3F+5F 整体，示意）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>口径 / 类别</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>科目</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>年化（示意）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>园区空间盘（甲方）</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>3F 办公租金 2850㎡</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>约 400 万（85% 去化 · ~4.5 元/㎡/天）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>园区空间盘（甲方）</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>5F 展贸租金 + 物业</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>约 300 万（部分免租 · 订单扣点反哺）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>园区空间盘（甲方）</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>6600㎡ 物业费</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>约 200 万（1.0 元/㎡/天 计）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>园区空间盘（甲方）</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>空间盘合计</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>约 900 万/年（满租稳定期）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>运营平台（乙方）</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>固定服务费</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>约 146 万（运营 96 + 活动 30 + 媒体 10 + 挂牌）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>运营平台（乙方）</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>招商佣金</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>1 月租金/成交（约 30–50 万）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>运营平台（乙方）</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>增值 + 出海分成</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>约 150–450 万（联合公司）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>运营平台（乙方）</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>经营性 + 补贴</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>约 50–100 万（门票/培训/空间 + 载体奖励）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>运营平台（乙方）</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>平台收入合计</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>约 380–740 万/年（稳定期示意区间）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3735,7 +4426,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/proposal/chuangzhihui-6600-proposal.xlsx
+++ b/proposal/chuangzhihui-6600-proposal.xlsx
@@ -28,14 +28,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00 研判报告" sheetId="19" state="visible" r:id="rId19"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05b 招商运营计划" sheetId="20" state="visible" r:id="rId20"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05c 活动日历" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10b 政策申报收入" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10c 会客厅测算" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10d 企业服务测算" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11f 大湾区出海资源" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11g 战略资源探讨" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11d 营收-收入结构" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11e 营收-成本盈亏" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 风险应对" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10e 出海费用清单" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10b 政策申报收入" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10c 会客厅测算" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10d 企业服务测算" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11f 大湾区出海资源" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11g 战略资源探讨" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11d 营收-收入结构" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11e 营收-成本盈亏" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 风险应对" sheetId="30" state="visible" r:id="rId30"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2994,6 +2995,139 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>08 · 出海费用清单 · 挂牌/代运营/资源导入（轻运营，供甲方预算）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>费用项</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>金额（含单位）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>① 出海挂牌费</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>国家/北欧会客厅挂牌 + 领事资源背书 + 出海身份/牌照</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>10–20 万元（一次性/按牌）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>② 代运营费用</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>领英/谷歌/短剧/社媒 海外账号搭建与投放代运营（媒介费企业承担）</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>打包 15–30 万/年（或 1–3 万/月/家）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>③ 资源导入费用</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>大湾区/复旦系/高校/领事/买家团/IP 资源对接与导入</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>打包 10–20 万/年（或按项目 1–5 万/次）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>费用合计（示意）</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>一次性挂牌 + 年度（代运营+资源导入）</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>一次性 10–20 万；年度 25–50 万/年；首年约 35–70 万</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>不含撮合佣金与海外媒介投放费；活动/招人方式待定</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>撮合：平台利润 1–30 万/项目 + 落地 1%–3%（按成交另计）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3240,7 +3374,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3462,207 +3596,6 @@
       <c r="C13" s="4" t="inlineStr">
         <is>
           <t>收入 ~150–250 万，平台净 ~50–90 万/年（不高估，待确认）</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>08 · 财务测算 · 企业服务（项目/收费/成本）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>服务项目</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>收费（含单位）</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>成本（含单位）</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="36" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>工商注册 · 代账</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>注册引流免费；代账 3000–6000 元/年/家</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>第三方分成 + 人力</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>政策申报</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>普通 0.3–2 万/项；高企/专精特新 2–8 万/项；补贴成功费 到账 5%–15%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>人力 + 材料杂费</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>知识产权</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>商标 800–2000 元/件；软著 2000–5000 元/件；专利代理 5000–1 万/件</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>第三方分成</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>财税 · 法务</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>顾问 1–5 万/年/家</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>第三方分成</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>融资顾问</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>成功佣金 融资额 1%–3%</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>人力</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>出海撮合</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>平台利润 1–30 万/项目 + 落地佣金 1%–3%</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>出海团队（单列）</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>人力成本（必列示）</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>企业服务暂不设专职，按兼职/共享列示</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>约 15–30 万/年（社保+人力）</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>第三方分成 / 杂费</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>第三方服务分成 按收入 30%–50%</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>系统/材料杂费 约 2–5 万/年</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>合理预估</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>首年企业服务收入(不含出海) ~30–60 万</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>净利 ~10–25 万</t>
         </is>
       </c>
     </row>
@@ -3682,6 +3615,207 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>08 · 财务测算 · 企业服务（项目/收费/成本）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>服务项目</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>收费（含单位）</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>成本（含单位）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>工商注册 · 代账</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>注册引流免费；代账 3000–6000 元/年/家</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>第三方分成 + 人力</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>政策申报</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>普通 0.3–2 万/项；高企/专精特新 2–8 万/项；补贴成功费 到账 5%–15%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>人力 + 材料杂费</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>知识产权</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>商标 800–2000 元/件；软著 2000–5000 元/件；专利代理 5000–1 万/件</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>第三方分成</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>财税 · 法务</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>顾问 1–5 万/年/家</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>第三方分成</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>融资顾问</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>成功佣金 融资额 1%–3%</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>人力</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>出海撮合</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>平台利润 1–30 万/项目 + 落地佣金 1%–3%</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>出海团队（单列）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>人力成本（必列示）</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>企业服务暂不设专职，按兼职/共享列示</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>约 15–30 万/年（社保+人力）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>第三方分成 / 杂费</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>第三方服务分成 按收入 30%–50%</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>系统/材料杂费 约 2–5 万/年</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>合理预估</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>首年企业服务收入(不含出海) ~30–60 万</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>净利 ~10–25 万</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3874,7 +4008,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3994,207 +4128,6 @@
       <c r="C7" s="4" t="inlineStr">
         <is>
           <t>本页为探讨方向，不构成承诺</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="58" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>08 · 营收逻辑 · 收入结构（3F+5F 整体，示意）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>口径 / 类别</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>科目</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>年化（示意）</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>园区空间盘（甲方）</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>3F 办公租金 2850㎡</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>约 400 万（85% 去化 · ~4.5 元/㎡/天）</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>园区空间盘（甲方）</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>5F 展贸租金 + 物业</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>约 300 万（部分免租 · 订单扣点反哺）</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>园区空间盘（甲方）</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>6600㎡ 物业费</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>约 200 万（1.0 元/㎡/天 计）</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>园区空间盘（甲方）</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>空间盘合计</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>约 900 万/年（满租稳定期）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>运营平台（乙方）</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>固定服务费</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>约 146 万（运营 96 + 活动 30 + 媒体 10 + 挂牌）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>运营平台（乙方）</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>招商佣金</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>1 月租金/成交（约 30–50 万）</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>运营平台（乙方）</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>增值 + 出海分成</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>约 150–450 万（联合公司）</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>运营平台（乙方）</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>经营性 + 补贴</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>约 50–100 万（门票/培训/空间 + 载体奖励）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>运营平台（乙方）</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>平台收入合计</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>约 380–740 万/年（稳定期示意区间）</t>
         </is>
       </c>
     </row>
@@ -4214,205 +4147,188 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="56" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>08 · 营收逻辑 · 成本结构与盈亏测算（示意）</t>
+          <t>08 · 营收逻辑 · 收入结构（3F+5F 整体，示意）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>项目</t>
+          <t>口径 / 类别</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>口径 / 金额</t>
+          <t>科目</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>说明</t>
+          <t>年化（示意）</t>
         </is>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>团队人力</t>
+          <t>园区空间盘（甲方）</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>100–180 万/年</t>
+          <t>3F 办公租金 2850㎡</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>在地 2 + 出海 1–3 + 兼职</t>
+          <t>约 400 万（85% 去化 · ~4.5 元/㎡/天）</t>
         </is>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>活动执行</t>
+          <t>园区空间盘（甲方）</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>约 30 万/年</t>
+          <t>5F 展贸租金 + 物业</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>约 30 场，含导师与物料</t>
+          <t>约 300 万（部分免租 · 订单扣点反哺）</t>
         </is>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>媒体 + 网络投流</t>
+          <t>园区空间盘（甲方）</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>约 10 万/年</t>
+          <t>6600㎡ 物业费</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>官媒 5 + 自媒体/投流 5</t>
+          <t>约 200 万（1.0 元/㎡/天 计）</t>
         </is>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>运营杂费/差旅/办公</t>
+          <t>园区空间盘（甲方）</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>20–40 万/年</t>
+          <t>空间盘合计</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>日常运营</t>
+          <t>约 900 万/年（满租稳定期）</t>
         </is>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>硬件装修摊销</t>
+          <t>运营平台（乙方）</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>甲方为主</t>
+          <t>固定服务费</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>乙方轻资产，前期投入低</t>
+          <t>约 146 万（运营 96 + 活动 30 + 媒体 10 + 挂牌）</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>成本合计</t>
+          <t>运营平台（乙方）</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>约 160–260 万/年</t>
+          <t>招商佣金</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>运营平台口径</t>
+          <t>1 月租金/成交（约 30–50 万）</t>
         </is>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>情景·保守</t>
+          <t>运营平台（乙方）</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>净 +195 万</t>
+          <t>增值 + 出海分成</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>收入 ~380 万 − 成本 ~185 万</t>
+          <t>约 150–450 万（联合公司）</t>
         </is>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>情景·中性</t>
+          <t>运营平台（乙方）</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>净 +300 万</t>
+          <t>经营性 + 补贴</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>收入 ~520 万 − 成本 ~220 万</t>
+          <t>约 50–100 万（门票/培训/空间 + 载体奖励）</t>
         </is>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>情景·乐观</t>
+          <t>运营平台（乙方）</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>净 +480 万</t>
+          <t>平台收入合计</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>收入 ~740 万 − 成本 ~260 万</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>盈亏与现金流</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>保底 96 万/年</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>三情景净收益均为正；出海撮合为最大增长弹性</t>
+          <t>约 380–740 万/年（稳定期示意区间）</t>
         </is>
       </c>
     </row>
@@ -4432,95 +4348,211 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="74" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="56" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>风险点与应对</t>
+          <t>08 · 营收逻辑 · 成本结构与盈亏测算（示意）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>风险</t>
+          <t>项目</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>应对</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
+          <t>口径 / 金额</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>空间合规（用途/消防/承重/用电）</t>
+          <t>团队人力</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>入驻准入审核；以轻型研发/中试/装配/测试与办公展示为主，拒高污染高噪音高能耗</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
+          <t>100–180 万/年</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>在地 2 + 出海 1–3 + 兼职</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>招商去化</t>
+          <t>活动执行</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>先样板企业 + 首批优惠 + 高校/协会/社群/复旦科技园渠道 + 政策抓手；对赌 60/70/85%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
+          <t>约 30 万/年</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>约 30 场，含导师与物料</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>收益周期</t>
+          <t>媒体 + 网络投流</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>基础运营费保障；佣金与去化挂钩；增值服务逐步导入，避免前期重投入</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
+          <t>约 10 万/年</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>官媒 5 + 自媒体/投流 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>政策兑现</t>
+          <t>运营杂费/差旅/办公</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>一切以政府最新文件为准；不承诺必得补贴；服务以辅导/申报/对接为主，成功费按实际兑现计</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
+          <t>20–40 万/年</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>日常运营</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>合作复制边界</t>
+          <t>硬件装修摊销</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>协同周边 ≤2 个项目；单项目单核算，避免人力成本覆盖不住</t>
+          <t>甲方为主</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>乙方轻资产，前期投入低</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>成本合计</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>约 160–260 万/年</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>运营平台口径</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>情景·保守</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>净 +195 万</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>收入 ~380 万 − 成本 ~185 万</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>情景·中性</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>净 +300 万</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>收入 ~520 万 − 成本 ~220 万</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>情景·乐观</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>净 +480 万</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>收入 ~740 万 − 成本 ~260 万</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>盈亏与现金流</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>保底 96 万/年</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>三情景净收益均为正；出海撮合为最大增长弹性</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
@@ -4705,6 +4737,108 @@
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="74" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>风险点与应对</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>风险</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>应对</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>空间合规（用途/消防/承重/用电）</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>入驻准入审核；以轻型研发/中试/装配/测试与办公展示为主，拒高污染高噪音高能耗</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>招商去化</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>先样板企业 + 首批优惠 + 高校/协会/社群/复旦科技园渠道 + 政策抓手；对赌 60/70/85%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>收益周期</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>基础运营费保障；佣金与去化挂钩；增值服务逐步导入，避免前期重投入</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>政策兑现</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>一切以政府最新文件为准；不承诺必得补贴；服务以辅导/申报/对接为主，成功费按实际兑现计</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>合作复制边界</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>协同周边 ≤2 个项目；单项目单核算，避免人力成本覆盖不住</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>

--- a/proposal/chuangzhihui-6600-proposal.xlsx
+++ b/proposal/chuangzhihui-6600-proposal.xlsx
@@ -28,15 +28,19 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00 研判报告" sheetId="19" state="visible" r:id="rId19"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05b 招商运营计划" sheetId="20" state="visible" r:id="rId20"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05c 活动日历" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10e 出海费用清单" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10b 政策申报收入" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10c 会客厅测算" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10d 企业服务测算" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11f 大湾区出海资源" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11g 战略资源探讨" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11d 营收-收入结构" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11e 营收-成本盈亏" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 风险应对" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07b 收费点价值论证" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10a 政策申报能力" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10c2 会客厅收益机制" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11h 国际英才+运营" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10e 出海费用清单" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10b 政策申报收入" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10c 会客厅测算" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10d 企业服务测算" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11f 大湾区出海资源" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11g 战略资源探讨" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11d 营收-收入结构" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11e 营收-成本盈亏" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 风险应对" sheetId="34" state="visible" r:id="rId34"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2995,6 +2999,669 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>07 · 收费点价值论证（逻辑/价值/怎么做）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>收费点</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>背后逻辑（凭什么）</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>给中建的可衡量价值</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>怎么做</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>招商佣金</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>牌照+政策+社群自带客流，110:1 漏斗</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>去化提速、租金回收提前</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>牌照锚定+政策礼包+社群/活动导流</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>活动 30 场/30 万</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>高频活动引流 + 完成载体 KPI</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>转化租客、补贴 10–20 万/年、媒体声量</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>6 类活动打包，投流引流→线下转化</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>媒体 10 万</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>官媒背书 + 自媒体投流</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>项目背书、招商曝光 ≥150 万</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>官媒 5 万 + 自媒体/投流 5 万</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>政策申报</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>挂牌科企服务中心+科企联+复旦系资质</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>企业补贴到账、平台服务费/分成</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>见政策申报能力与清单</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>企业服务</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>联合公司承接注册/申报/知产/财税</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>企业黏性、第二收入曲线</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>联合公司经营分成</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>出海撮合</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>领事/大湾区/高校/国际英才资源</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>海外订单、租金反哺、合资收益</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>全链条 + 领事路径</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>国际会客厅</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>领事资源合作方 + 高端背书</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>外资对接、高端招商、≥80 万收益</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>见会客厅收益逻辑与机制</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="82" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>08 · 政策申报能力与可申报清单</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>类别</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>凭什么能申（资质）</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>挂牌杨浦科技企业服务中心 + 依托科企联，政务快速通道</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>凭什么能申（资质）</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>拟入驻上海一网通办创新券平台，作服务机构核销</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>凭什么能申（资质）</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>复旦系（技术转移/珠海院/成果转化中心）+ 高校资源</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>凭什么能申（资质）</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>专业申报团队与过往经验；载体认定路径（载体/成果转化平台/OPC 社区）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>本项目可申（企业侧）</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>高企 20 万、专精特新 10/30 万、科小备案、研发加计</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>本项目可申（企业侧）</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>AI/大数据房租补贴 ≤100 万/年、算力补贴 ≤50%、创新券 ≤30 万/年、微短剧专项</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>本项目可申（载体侧）</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>成果转化平台运营补贴 ≤100 万/年、服务业引导资金 ≤300 万、活动/载体补贴（满年 10–20 万）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>政策→收入（平台现金）</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>申报服务费（科小 0.3–2 万/家；高企/专精特新 2–8 万/家）+ 成功分成（到账 5%–15%）+ 载体运营补贴（10–20 万/年）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>前提</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>先取得相应认定（载体/服务机构）；先跑通 3–5 家样板形成可复制流水</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>08 · 国际会客厅收益逻辑与合作机制（≥80 万）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>项</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>口径</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>年收益（保守）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="34" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>合作机制</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>平台(运营+活动+撮合) × 领事资源合作方(网络+空间) × 复旦/科企联(背书+获客)，按项目分润</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>国家/联合冠名</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>1 个 × 30–80 万/年</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>约 40 万</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>企业常驻会籍</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>3–5 家 × 10 万/家/年</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>约 30–50 万</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>单场活动（领事出席）</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>6–8 场 × 3–8 万/场</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>约 20–40 万</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>出海对接服务</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>单国服务包 20–50 万/项目 × 1–2 单</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>约 20–50 万</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>合计（毛收益）</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>以上累计</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>约 110–180 万 → 分润/成本后平台 ≥80 万</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>给中建价值</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>以国家为单位的招商与外资对接入口、高端背书与外事资源</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="84" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>08 · 出海板块补充 · 国际英才（沪动营）+ 出海运营</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>板块</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>国际英才·定位</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>「沪联世界·智创未来」财大/复旦/同济三校联合，服务逾万名留学生，培养一带一路桥梁人才</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>三大体系</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>思想引领（丝路青年领袖峰会）→ 能力提升（1+N 双导师·跨境电商实训）→ 实践转化（跨境贸易服务中心·全球供应链）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>出海用途</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>双语双市场人才、TikTok 直播选品、海外品牌孵化、连接一带一路国家母国市场</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>百千万工程(3年)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>孵化 100 跨境团队 / 促成 1000 人就业 / 培养 10000 复合人才；目标 10 亿跨境贸易、30 海外品牌</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>国际英才收入落点</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>训练营/创投大赛/跨境撮合佣金/企业结对 + 留学生政策项目</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>出海运营·内容</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>领英/谷歌/TikTok/短剧代运营、海外账号搭建与投放、出海活动与买家团/展销运营、落地陪跑</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>出海运营·团队</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>初期各部门抽调兼职 → 成熟设全职约 3 人</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>出海运营·收费</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>出海专项服务费 + 代运营 + 撮合佣金</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3122,7 +3789,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3374,7 +4041,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3596,739 +4263,6 @@
       <c r="C13" s="4" t="inlineStr">
         <is>
           <t>收入 ~150–250 万，平台净 ~50–90 万/年（不高估，待确认）</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>08 · 财务测算 · 企业服务（项目/收费/成本）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>服务项目</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>收费（含单位）</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>成本（含单位）</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="36" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>工商注册 · 代账</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>注册引流免费；代账 3000–6000 元/年/家</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>第三方分成 + 人力</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>政策申报</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>普通 0.3–2 万/项；高企/专精特新 2–8 万/项；补贴成功费 到账 5%–15%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>人力 + 材料杂费</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>知识产权</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>商标 800–2000 元/件；软著 2000–5000 元/件；专利代理 5000–1 万/件</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>第三方分成</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>财税 · 法务</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>顾问 1–5 万/年/家</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>第三方分成</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>融资顾问</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>成功佣金 融资额 1%–3%</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>人力</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>出海撮合</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>平台利润 1–30 万/项目 + 落地佣金 1%–3%</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>出海团队（单列）</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>人力成本（必列示）</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>企业服务暂不设专职，按兼职/共享列示</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>约 15–30 万/年（社保+人力）</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>第三方分成 / 杂费</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>第三方服务分成 按收入 30%–50%</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>系统/材料杂费 约 2–5 万/年</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>合理预估</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>首年企业服务收入(不含出海) ~30–60 万</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>净利 ~10–25 万</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:B15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="78" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>08 · 大湾区出海资源叠加（复旦系 + 高校，沪穗联动）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>资源</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>能力 / 说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="38" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>复旦珠海创新研究院</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>九大公共平台（集成电路/大数据智算/工业仿真/海洋科技/物联网智慧城市/先进材料）；手心研发·手背转化；服务横琴粤澳深合区</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="38" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>中国—葡语国家科技合作平台</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>横琴对接葡语系（巴西/葡萄牙/安哥拉/莫桑比克）唯一国家级平台；市场调研·本地匹配·海外展会·合规咨询</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="38" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>珠澳双循环出海窗口</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>澳门自由港 + 葡语商贸平台；内地研发+澳门展销+葡语国家落地；海外总部/海外仓中转，规避关税壁垒</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="38" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>海洋科技/物联网海外转化</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>海洋监测/智慧城市物联网经横琴出口东南亚、拉美沿海；海外项目联合申报、海外工程落地</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="38" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>复旦广州校友会</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>广州本地校友网络与资源对接</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="38" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>粤港澳大湾区精准医学研究院</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>省市南沙复旦联和健康五方共建；南沙唯一万笼级实验动物中心；肿瘤/代谢/生殖精准诊疗、类器官、医疗器械转化</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="38" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>深圳复旦研究院</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>河套深港科创合作区；AI/前沿医学/集成电路；联动香港，打通深港产学研</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="38" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>粤港澳复旦科技成果转化服务中心</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>复旦技术转移落地南沙；技术授权海外/海外联合研发/国际专利；对接新加坡·英·美医学机构；海外临床申报与国际认证</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="38" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>港澳跨境协同通道</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>联动香港生物医药创新协会/香港科技园；海外样品通关·市场准入·投融资路演；长三角-大湾区-海外对接会</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="38" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>出海基金矩阵</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>粤科复旦母基金、南沙科创产业基金；海外建厂/分销/研发中心；跨境股权融资、跨境担保</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="38" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>暨南大学 / 华侨大学</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>侨校资源，服务东南亚等海外华人华侨市场</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="38" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>广东外语外贸大学</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>出海第一梯队：小语种（东盟/葡语/西语）·海丝国别智库·跨境合规·国际贸易·海外市场调研</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="38" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>广州大学黄埔研究院</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>数字经济·跨境新媒体·海外独立站·智能制造国际转化</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>08 · 战略资源探讨（东方枢纽/谷歌/领英，待落实）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>资源</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>探讨方向</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>在项目中的作用</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="40" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>东方枢纽</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>国际商务合作区 + 综保区 + 空铁枢纽</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>出海企业境内关外通道、保税展示、国际中转与海外仓承接点</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="40" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>谷歌 Google</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Google Ads / YouTube 出海投放；谷歌在领事馆/国别活动中的技术与流量角色</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>叠加海外数字营销通路，服务内容与货品出海</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>领英 LinkedIn</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>B2B 海外决策人触达、品牌出海、海外招募</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>国际出海职能线上主通路之一，与展会/领事撮合互补</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>收费落点</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>出海专项服务费 + 撮合佣金 + 海外营销投放代运营 + 国家会客厅冠名/会籍</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>强化国际出海职能并在出海板块收费</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="40" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>东方枢纽与谷歌合作以实际对接结果为准</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>本页为探讨方向，不构成承诺</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="58" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>08 · 营收逻辑 · 收入结构（3F+5F 整体，示意）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>口径 / 类别</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>科目</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>年化（示意）</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>园区空间盘（甲方）</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>3F 办公租金 2850㎡</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>约 400 万（85% 去化 · ~4.5 元/㎡/天）</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>园区空间盘（甲方）</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>5F 展贸租金 + 物业</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>约 300 万（部分免租 · 订单扣点反哺）</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>园区空间盘（甲方）</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>6600㎡ 物业费</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>约 200 万（1.0 元/㎡/天 计）</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>园区空间盘（甲方）</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>空间盘合计</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>约 900 万/年（满租稳定期）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>运营平台（乙方）</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>固定服务费</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>约 146 万（运营 96 + 活动 30 + 媒体 10 + 挂牌）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>运营平台（乙方）</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>招商佣金</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>1 月租金/成交（约 30–50 万）</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>运营平台（乙方）</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>增值 + 出海分成</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>约 150–450 万（联合公司）</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>运营平台（乙方）</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>经营性 + 补贴</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>约 50–100 万（门票/培训/空间 + 载体奖励）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>运营平台（乙方）</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>平台收入合计</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>约 380–740 万/年（稳定期示意区间）</t>
         </is>
       </c>
     </row>
@@ -4348,205 +4282,188 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="56" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>08 · 营收逻辑 · 成本结构与盈亏测算（示意）</t>
+          <t>08 · 财务测算 · 企业服务（项目/收费/成本）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>项目</t>
+          <t>服务项目</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>口径 / 金额</t>
+          <t>收费（含单位）</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
+          <t>成本（含单位）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>团队人力</t>
+          <t>工商注册 · 代账</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>100–180 万/年</t>
+          <t>注册引流免费；代账 3000–6000 元/年/家</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>在地 2 + 出海 1–3 + 兼职</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
+          <t>第三方分成 + 人力</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>活动执行</t>
+          <t>政策申报</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>约 30 万/年</t>
+          <t>普通 0.3–2 万/项；高企/专精特新 2–8 万/项；补贴成功费 到账 5%–15%</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>约 30 场，含导师与物料</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="32" customHeight="1">
+          <t>人力 + 材料杂费</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>媒体 + 网络投流</t>
+          <t>知识产权</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>约 10 万/年</t>
+          <t>商标 800–2000 元/件；软著 2000–5000 元/件；专利代理 5000–1 万/件</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>官媒 5 + 自媒体/投流 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1">
+          <t>第三方分成</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>运营杂费/差旅/办公</t>
+          <t>财税 · 法务</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>20–40 万/年</t>
+          <t>顾问 1–5 万/年/家</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>日常运营</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
+          <t>第三方分成</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>硬件装修摊销</t>
+          <t>融资顾问</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>甲方为主</t>
+          <t>成功佣金 融资额 1%–3%</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>乙方轻资产，前期投入低</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="32" customHeight="1">
+          <t>人力</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>成本合计</t>
+          <t>出海撮合</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>约 160–260 万/年</t>
+          <t>平台利润 1–30 万/项目 + 落地佣金 1%–3%</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>运营平台口径</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="32" customHeight="1">
+          <t>出海团队（单列）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>情景·保守</t>
+          <t>人力成本（必列示）</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>净 +195 万</t>
+          <t>企业服务暂不设专职，按兼职/共享列示</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>收入 ~380 万 − 成本 ~185 万</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="32" customHeight="1">
+          <t>约 15–30 万/年（社保+人力）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>情景·中性</t>
+          <t>第三方分成 / 杂费</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>净 +300 万</t>
+          <t>第三方服务分成 按收入 30%–50%</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>收入 ~520 万 − 成本 ~220 万</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1">
+          <t>系统/材料杂费 约 2–5 万/年</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>情景·乐观</t>
+          <t>合理预估</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>净 +480 万</t>
+          <t>首年企业服务收入(不含出海) ~30–60 万</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>收入 ~740 万 − 成本 ~260 万</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>盈亏与现金流</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>保底 96 万/年</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>三情景净收益均为正；出海撮合为最大增长弹性</t>
+          <t>净利 ~10–25 万</t>
         </is>
       </c>
     </row>
@@ -4745,6 +4662,756 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="78" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>08 · 大湾区出海资源叠加（复旦系 + 高校，沪穗联动）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>资源</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>能力 / 说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="38" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>复旦珠海创新研究院</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>九大公共平台（集成电路/大数据智算/工业仿真/海洋科技/物联网智慧城市/先进材料）；手心研发·手背转化；服务横琴粤澳深合区</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="38" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>中国—葡语国家科技合作平台</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>横琴对接葡语系（巴西/葡萄牙/安哥拉/莫桑比克）唯一国家级平台；市场调研·本地匹配·海外展会·合规咨询</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="38" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>珠澳双循环出海窗口</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>澳门自由港 + 葡语商贸平台；内地研发+澳门展销+葡语国家落地；海外总部/海外仓中转，规避关税壁垒</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="38" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>海洋科技/物联网海外转化</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>海洋监测/智慧城市物联网经横琴出口东南亚、拉美沿海；海外项目联合申报、海外工程落地</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="38" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>复旦广州校友会</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>广州本地校友网络与资源对接</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="38" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>粤港澳大湾区精准医学研究院</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>省市南沙复旦联和健康五方共建；南沙唯一万笼级实验动物中心；肿瘤/代谢/生殖精准诊疗、类器官、医疗器械转化</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="38" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>深圳复旦研究院</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>河套深港科创合作区；AI/前沿医学/集成电路；联动香港，打通深港产学研</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="38" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>粤港澳复旦科技成果转化服务中心</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>复旦技术转移落地南沙；技术授权海外/海外联合研发/国际专利；对接新加坡·英·美医学机构；海外临床申报与国际认证</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="38" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>港澳跨境协同通道</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>联动香港生物医药创新协会/香港科技园；海外样品通关·市场准入·投融资路演；长三角-大湾区-海外对接会</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="38" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>出海基金矩阵</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>粤科复旦母基金、南沙科创产业基金；海外建厂/分销/研发中心；跨境股权融资、跨境担保</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="38" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>暨南大学 / 华侨大学</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>侨校资源，服务东南亚等海外华人华侨市场</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="38" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>广东外语外贸大学</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>出海第一梯队：小语种（东盟/葡语/西语）·海丝国别智库·跨境合规·国际贸易·海外市场调研</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="38" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>广州大学黄埔研究院</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>数字经济·跨境新媒体·海外独立站·智能制造国际转化</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>08 · 战略资源探讨（东方枢纽/谷歌/领英，待落实）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>资源</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>探讨方向</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>在项目中的作用</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>东方枢纽</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>国际商务合作区 + 综保区 + 空铁枢纽</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>出海企业境内关外通道、保税展示、国际中转与海外仓承接点</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>谷歌 Google</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Google Ads / YouTube 出海投放；谷歌在领事馆/国别活动中的技术与流量角色</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>叠加海外数字营销通路，服务内容与货品出海</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>领英 LinkedIn</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>B2B 海外决策人触达、品牌出海、海外招募</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>国际出海职能线上主通路之一，与展会/领事撮合互补</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>收费落点</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>出海专项服务费 + 撮合佣金 + 海外营销投放代运营 + 国家会客厅冠名/会籍</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>强化国际出海职能并在出海板块收费</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>东方枢纽与谷歌合作以实际对接结果为准</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>本页为探讨方向，不构成承诺</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>08 · 营收逻辑 · 收入结构（3F+5F 整体，示意）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>口径 / 类别</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>科目</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>年化（示意）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>园区空间盘（甲方）</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>3F 办公租金 2850㎡</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>约 400 万（85% 去化 · ~4.5 元/㎡/天）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>园区空间盘（甲方）</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>5F 展贸租金 + 物业</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>约 300 万（部分免租 · 订单扣点反哺）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>园区空间盘（甲方）</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>6600㎡ 物业费</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>约 200 万（1.0 元/㎡/天 计）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>园区空间盘（甲方）</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>空间盘合计</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>约 900 万/年（满租稳定期）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>运营平台（乙方）</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>固定服务费</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>约 146 万（运营 96 + 活动 30 + 媒体 10 + 挂牌）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>运营平台（乙方）</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>招商佣金</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>1 月租金/成交（约 30–50 万）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>运营平台（乙方）</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>增值 + 出海分成</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>约 150–450 万（联合公司）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>运营平台（乙方）</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>经营性 + 补贴</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>约 50–100 万（门票/培训/空间 + 载体奖励）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>运营平台（乙方）</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>平台收入合计</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>约 380–740 万/年（稳定期示意区间）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="56" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>08 · 营收逻辑 · 成本结构与盈亏测算（示意）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>项目</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>口径 / 金额</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>团队人力</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>100–180 万/年</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>在地 2 + 出海 1–3 + 兼职</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>活动执行</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>约 30 万/年</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>约 30 场，含导师与物料</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>媒体 + 网络投流</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>约 10 万/年</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>官媒 5 + 自媒体/投流 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>运营杂费/差旅/办公</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>20–40 万/年</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>日常运营</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>硬件装修摊销</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>甲方为主</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>乙方轻资产，前期投入低</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>成本合计</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>约 160–260 万/年</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>运营平台口径</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>情景·保守</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>净 +195 万</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>收入 ~380 万 − 成本 ~185 万</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>情景·中性</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>净 +300 万</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>收入 ~520 万 − 成本 ~220 万</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>情景·乐观</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>净 +480 万</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>收入 ~740 万 − 成本 ~260 万</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>盈亏与现金流</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>保底 96 万/年</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>三情景净收益均为正；出海撮合为最大增长弹性</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
